--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,11 +79,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -449,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB52"/>
+  <dimension ref="A1:AB51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -630,623 +636,617 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AIMTRON</t>
+          <t>NIRLON</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AIMTRON</t>
+          <t>Nirlon Limited</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3608</v>
+        <v>5821</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>78.5</v>
+        <v>16.3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1731.15</v>
+        <v>642.1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1731.15</v>
+        <v>647.95</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>107.41</v>
-      </c>
+        <v>4.84</v>
+      </c>
+      <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n">
-        <v>156.79</v>
+        <v>17.74</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>4.03</v>
+        <v>3.07</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+        <v>3.57</v>
+      </c>
+      <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n">
-        <v>152.8</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>160.6</v>
-      </c>
+        <v>14.7</v>
+      </c>
+      <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n">
-        <v>46</v>
+        <v>357</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SJS</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>S.J.S. Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>8111</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>OBSCP</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>OBSCP</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>2532.5</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>2532.5</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>115.28</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>860.15</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>175.61</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>165.63</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>163.4</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>KESAR</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>KESAR INDIA LIMITED</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3956</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1266.1</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>1284.85</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>14.27</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>94.78</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SHADOWFAX</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>15180</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>260.34</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>264.84</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>122.63</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>136.71</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>PRICOLLTD</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Pricol Limited</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>The Karnataka Bank Limited</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Auto</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>9654</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>792.05</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>792.05</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>25.04</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>85.04000000000001</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>268</v>
-      </c>
-      <c r="W5" s="2" t="n">
-        <v>251</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>12611</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>335.05</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>93.81999999999999</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1437</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>1341</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>ROSSTECH</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Rossell Techsys Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Standard Engineering Technology Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>4047</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1073.45</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1094.5</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>75.76000000000001</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="n">
+        <v>6136</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>127.12</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>147.88</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>AFCOM</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Afcom Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CFF</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>CFF FLUID CONTROL LIMITED</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>4311</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
+      <c r="F7" s="3" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>1502.05</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1502.05</v>
-      </c>
-      <c r="L7" s="2" t="n">
+      <c r="J7" s="3" t="n">
+        <v>1041.85</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1041.85</v>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>66.34</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>65.04000000000001</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T7" s="2" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>92.22</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MANINDS</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Man Industries (India) Limited</t>
+          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1273,65 +1273,69 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4496</v>
+        <v>8921</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>22</v>
+        <v>49.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>599.45</v>
+        <v>907.55</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>601.4</v>
+        <v>925.15</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.32</v>
+        <v>-1.9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>7.02</v>
+        <v>13.33</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>41.33</v>
+        <v>31.39</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>51.22</v>
+        <v>28.42</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S8" s="2" t="n"/>
+        <v>2.41</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>11.27</v>
+      </c>
       <c r="T8" s="2" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="U8" s="2" t="n"/>
+        <v>26.4</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>17.2</v>
+      </c>
       <c r="V8" s="2" t="n">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
@@ -1350,7 +1354,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1364,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>BLUECLOUDS</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CORONA Remedies Limited</t>
+          <t>Blue Cloud Softech Solutions Limited</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1375,69 +1379,61 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>13071</v>
+        <v>2116</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>61.6</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2137.1</v>
+        <v>22.98</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2159.7</v>
+        <v>22.98</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>34.15</v>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n">
-        <v>48.57</v>
+        <v>0.57</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>-0.55</v>
+        <v>0.17</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>12.2</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="S9" s="2" t="n"/>
       <c r="T9" s="2" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>36.4</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="U9" s="2" t="n"/>
       <c r="V9" s="2" t="n">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
@@ -1456,111 +1452,107 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KHAZANCHI</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Khazanchi Jewellers Limited</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1961</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>792.45</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>792.45</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>31.69</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T10" s="2" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="W10" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>KMEW</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Knowledge Marine &amp; Engineering Works Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>6793</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2712.7</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>2756.5</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>24.76</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>184.11</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1572,12 +1564,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Manorama Industries Limited</t>
+          <t>Aeroflex Industries Limited</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1587,69 +1579,65 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Nifty FMCG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>10965</v>
+        <v>6644</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>42.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1737.1</v>
+        <v>504.25</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1737.1</v>
+        <v>510.9</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>33.05</v>
+        <v>24.47</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>23.17</v>
+        <v>129.55</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>26.21</v>
+        <v>180.64</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S11" s="2" t="n">
-        <v>-11.05</v>
-      </c>
+        <v>2.41</v>
+      </c>
+      <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>37.3</v>
-      </c>
+        <v>178.6</v>
+      </c>
+      <c r="U11" s="2" t="n"/>
       <c r="V11" s="2" t="n">
-        <v>258</v>
+        <v>67</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>226</v>
+        <v>56</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
@@ -1668,7 +1656,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1678,81 +1666,85 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>SHREEREF</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
+          <t>SHREE REFRIGERATIONS LIMITED</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6926</v>
+        <v>1486</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>53.5</v>
+        <v>69</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2730.8</v>
+        <v>399.65</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2730.8</v>
+        <v>405.4</v>
       </c>
       <c r="L12" s="2" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>118.93</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>121.78</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>38.07</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>227.22</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n">
-        <v>223.2</v>
-      </c>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>65</v>
-      </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
@@ -1760,17 +1752,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1772,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>INDOTECH</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Limited</t>
+          <t>Indo Tech Transformers Limited</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1799,65 +1791,65 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6585</v>
+        <v>4057</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>105</v>
+        <v>40.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1433.9</v>
+        <v>3850.6</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1433.9</v>
+        <v>3902.5</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>73.7</v>
+        <v>49.07</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>94.84</v>
+        <v>152.51</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>137.2</v>
+        <v>110.8</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>4.42</v>
+        <v>2.41</v>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n">
-        <v>133.2</v>
+        <v>108.8</v>
       </c>
       <c r="U13" s="2" t="n"/>
       <c r="V13" s="2" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1872,7 +1864,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1874,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1901,61 +1893,61 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5188</v>
+        <v>5638</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>79.8</v>
+        <v>46.1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>370.7</v>
+        <v>49.62</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>371.2</v>
+        <v>49.62</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>69.45999999999999</v>
+        <v>22.62</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>102.89</v>
+        <v>99.55</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>123.57</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>4.42</v>
+        <v>2.41</v>
       </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="2" t="n">
-        <v>119.5</v>
+        <v>95.2</v>
       </c>
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>10</v>
+        <v>18.4</v>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
@@ -1974,107 +1966,107 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>STYLAMIND</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Stylam Industries Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Madhya Bharat Agro Products Limited</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>6172</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>3642</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>3651.2</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>37.24</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>119.28</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="n">
-        <v>115.2</v>
-      </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="W15" s="2" t="n">
+      <c r="F15" s="3" t="n">
+        <v>7479</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>168.91</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>170.69</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>84.09</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>94.98</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="W15" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="X15" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="X15" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2086,12 +2078,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>BLUSPRING</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Azad Engineering Limited</t>
+          <t>Bluspring Enterprises Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2105,62 +2097,60 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>17552</v>
+        <v>1852</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2717.8</v>
+        <v>133.01</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2717.8</v>
+        <v>133.01</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>29.53</v>
+        <v>81.11</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>72.11</v>
+        <v>123.09</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>75.25</v>
+        <v>64.23</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>4.42</v>
+        <v>2.41</v>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n">
-        <v>71.2</v>
+        <v>62.2</v>
       </c>
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n">
-        <v>140</v>
+        <v>-17.5</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="X16" s="2" t="n">
-        <v>4.5</v>
-      </c>
+        <v>-23</v>
+      </c>
+      <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
@@ -2178,7 +2168,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2188,99 +2178,103 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>STEELCAS</t>
+          <t>AIRFLOA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Steelcast Limited</t>
+          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>3561</v>
+        <v>1026</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>39.3</v>
+        <v>26.2</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>351.85</v>
+        <v>434</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>354.15</v>
+        <v>434</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>24.28</v>
+        <v>37.62</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>56.9</v>
+        <v>60.47</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>69.08</v>
+        <v>55.39</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>4.03</v>
+        <v>-0.03</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S17" s="2" t="n"/>
+        <v>0.36</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>-6.03</v>
+      </c>
       <c r="T17" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="U17" s="2" t="n"/>
+        <v>55.4</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>61.4</v>
+      </c>
       <c r="V17" s="2" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="X17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2290,17 +2284,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CFF</t>
+          <t>VINYAS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CFF FLUID CONTROL LIMITED</t>
+          <t>VINYAS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2309,62 +2303,62 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2142</v>
+        <v>2018</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>54.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1021.35</v>
+        <v>1603.15</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1023.7</v>
+        <v>1611.8</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.54</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>35.95</v>
+        <v>51.96</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>92.91</v>
+        <v>62.26</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>63.94</v>
+        <v>32.77</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>4.03</v>
+        <v>2.26</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>4.42</v>
+        <v>2.66</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>-3.8</v>
+        <v>-4.34</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>59.9</v>
+        <v>30.5</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>67.7</v>
+        <v>37.1</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="X18" s="2" t="n">
         <v>0</v>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2390,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>VISHNU</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Vishnu Chemicals Limited</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2411,73 +2405,69 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>17025</v>
+        <v>4303</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1386.7</v>
+        <v>637.7</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1393.6</v>
+        <v>640.45</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.43</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>32.75</v>
+        <v>7.04</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>50.76</v>
+        <v>24.46</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46.88</v>
+        <v>24.19</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S19" s="2" t="n">
-        <v>12.7</v>
-      </c>
+        <v>2.41</v>
+      </c>
+      <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>34.2</v>
-      </c>
+        <v>22.2</v>
+      </c>
+      <c r="U19" s="2" t="n"/>
       <c r="V19" s="2" t="n">
-        <v>603</v>
+        <v>150</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>565</v>
+        <v>142</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2492,7 +2482,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2492,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2521,65 +2511,65 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>17034</v>
+        <v>2074</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>38</v>
+        <v>11.1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>510.05</v>
+        <v>270.52</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>518</v>
+        <v>270.9</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-1.53</v>
+        <v>-0.14</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>23.16</v>
+        <v>21.97</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>14.55</v>
+        <v>25.74</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>16.13</v>
+        <v>17.89</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>4.42</v>
+        <v>2.41</v>
       </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="n">
-        <v>12.1</v>
+        <v>15.9</v>
       </c>
       <c r="U20" s="2" t="n"/>
       <c r="V20" s="2" t="n">
-        <v>444</v>
+        <v>186</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>404</v>
+        <v>161</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>9.9</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2594,7 +2584,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2604,88 +2594,76 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>TURTLEMINT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>Turtlemint Fintech Solutions Limited</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2202</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>70</v>
-      </c>
+        <v>4233</v>
+      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>852</v>
+        <v>147.89</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>852</v>
+        <v>150.15</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>126.75</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>182.07</v>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n">
-        <v>176.04</v>
+        <v>9.25</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>4.03</v>
+        <v>2.23</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+        <v>2.39</v>
+      </c>
+      <c r="S21" s="2" t="n"/>
       <c r="T21" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>179.8</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="U21" s="2" t="n"/>
       <c r="V21" s="2" t="n">
-        <v>31.5</v>
+        <v>-144</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="X21" s="2" t="n">
-        <v>16.7</v>
-      </c>
+        <v>-145</v>
+      </c>
+      <c r="X21" s="2" t="n"/>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2700,7 +2678,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2688,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2729,184 +2707,184 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2065</v>
+        <v>1157</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>71.8</v>
+        <v>55.7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>950.25</v>
+        <v>1020.3</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>967.6</v>
+        <v>1020.3</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-1.79</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>81.73</v>
+        <v>57.38</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>105.55</v>
+        <v>229.13</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>137.56</v>
+        <v>261.68</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>4.03</v>
+        <v>2.26</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>4.42</v>
+        <v>2.66</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>-3.8</v>
+        <v>-4.34</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>133.5</v>
+        <v>259.4</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>141.4</v>
+        <v>266</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>DIVGIITTS</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>COMSYN</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Commercial Syn Bags Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>3979</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
+      <c r="F23" s="3" t="n">
+        <v>1169</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="2" t="n">
-        <v>1301.05</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>1301.05</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>95.94</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>74.73999999999999</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>101.34</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="W23" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="X23" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="J23" s="3" t="n">
+        <v>289.17</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>289.77</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>86.53</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>109.39</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AB23" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2918,12 +2896,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SPR Auto Technologies Limited</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2933,69 +2911,65 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nifty Auto</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>19789</v>
+        <v>1594</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>33.9</v>
+        <v>32.6</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4492.4</v>
+        <v>502.35</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>4524.4</v>
+        <v>511.85</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>-0.71</v>
+        <v>-1.86</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>32.69</v>
+        <v>49.36</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>45.67</v>
+        <v>104.43</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>82.65000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S24" s="2" t="n">
-        <v>21.1</v>
-      </c>
+        <v>2.41</v>
+      </c>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <v>61.6</v>
-      </c>
+        <v>94.2</v>
+      </c>
+      <c r="U24" s="2" t="n"/>
       <c r="V24" s="2" t="n">
-        <v>575</v>
+        <v>56</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>562</v>
+        <v>51</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>2.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
@@ -3014,7 +2988,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3024,12 +2998,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3039,69 +3013,65 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>11714</v>
+        <v>1945</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>8.15</v>
+        <v>28.8</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>309.65</v>
+        <v>271.32</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>313.7</v>
+        <v>271.32</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-1.29</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>25.82</v>
+        <v>54.38</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>52.75</v>
+        <v>69.47</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>82.26000000000001</v>
+        <v>79.27</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S25" s="2" t="n">
-        <v>-0.45</v>
-      </c>
+        <v>2.41</v>
+      </c>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U25" s="2" t="n">
-        <v>82.7</v>
-      </c>
+        <v>77.3</v>
+      </c>
+      <c r="U25" s="2" t="n"/>
       <c r="V25" s="2" t="n">
-        <v>1437</v>
+        <v>67</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>1341</v>
+        <v>64</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3090,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3100,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+          <t>Timex Group India Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3149,65 +3119,63 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>9611</v>
+        <v>5983</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>99.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1468.3</v>
+        <v>595.25</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1468.3</v>
+        <v>599.95</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>105.3</v>
-      </c>
+        <v>58.42</v>
+      </c>
+      <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n">
-        <v>72.13</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>4.03</v>
+        <v>3.07</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>4.42</v>
+        <v>3.57</v>
       </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="2" t="n">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>27.6</v>
+        <v>13.3</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3222,7 +3190,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3200,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Ram Ratna Wires Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3251,61 +3219,61 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>4435</v>
+        <v>9130</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>34.3</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>475.05</v>
+        <v>4232</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>475.05</v>
+        <v>4232</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>52.24</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>39.18</v>
+        <v>70.92</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>4.03</v>
+        <v>25.87</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>4.42</v>
+        <v>26.62</v>
       </c>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="2" t="n">
-        <v>35.1</v>
+        <v>45</v>
       </c>
       <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>17.4</v>
+        <v>3.5</v>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
@@ -3319,12 +3287,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3334,12 +3302,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>Gokul Agro Resources Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3349,65 +3317,69 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty FMCG</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>12967</v>
+        <v>7318</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1940.8</v>
+        <v>244.05</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1965.3</v>
+        <v>248.78</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-1.25</v>
+        <v>-1.9</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>46.69</v>
+        <v>8.5</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>84.13</v>
+        <v>43.61</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>131.67</v>
+        <v>48.4</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S28" s="2" t="n"/>
+        <v>2.41</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>-14.64</v>
+      </c>
       <c r="T28" s="2" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="U28" s="2" t="n"/>
+        <v>46.4</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>63</v>
+      </c>
       <c r="V28" s="2" t="n">
-        <v>134</v>
+        <v>421</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>113</v>
+        <v>370</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>18.6</v>
+        <v>13.8</v>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
@@ -3426,7 +3398,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3408,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SENORES</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Senores Pharmaceuticals Limited</t>
+          <t>Canara HSBC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3451,69 +3423,73 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>6805</v>
+        <v>14620</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>53.8</v>
+        <v>111</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
         <v>4</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1477.7</v>
+        <v>154.7</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1492.4</v>
+        <v>155.24</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>-0.98</v>
+        <v>-0.35</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>40.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>88.59</v>
+        <v>2.75</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>118.84</v>
+        <v>38.84</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>4.03</v>
+        <v>-0.37</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S29" s="2" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>-5.01</v>
+      </c>
       <c r="T29" s="2" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="U29" s="2" t="n"/>
+        <v>39.2</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>43.9</v>
+      </c>
       <c r="V29" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3528,7 +3504,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3538,199 +3514,207 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>ZELIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Creative Newtech Limited</t>
+          <t>Zelio E Mobility Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>1867</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>25.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1243</v>
+        <v>882.95</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1243</v>
+        <v>882.95</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>95.15000000000001</v>
+        <v>83.91</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>89.94</v>
+        <v>238.49</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>99.76000000000001</v>
+        <v>443.02</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>4.03</v>
+        <v>1.74</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S30" s="2" t="n"/>
+        <v>2.21</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>-4.4</v>
+      </c>
       <c r="T30" s="2" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="U30" s="2" t="n"/>
+        <v>441.3</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>447.4</v>
+      </c>
       <c r="V30" s="2" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Standard Engineering Technology Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>CORONA</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>CORONA Remedies Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>5953</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>298.4</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>300.05</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>118.88</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>127.08</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="W31" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="X31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>13109</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>2149</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>2165.8</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z31" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB31" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3742,12 +3726,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>ONEGLOBAL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Shadowfax Technologies Limited</t>
+          <t>One Global Service Provider Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3761,65 +3745,61 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>14742</v>
+        <v>1077</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>87.2</v>
+        <v>14.6</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>251.33</v>
+        <v>553.95</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>251.33</v>
+        <v>564.1</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>33.28</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>101.5</v>
-      </c>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n">
-        <v>128.52</v>
+        <v>3.14</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>2.22</v>
+        <v>0.17</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>3.03</v>
+        <v>0.18</v>
       </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="n">
-        <v>126.3</v>
+        <v>3</v>
       </c>
       <c r="U32" s="2" t="n"/>
       <c r="V32" s="2" t="n">
-        <v>169</v>
+        <v>74</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>50.9</v>
+        <v>5.7</v>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -3834,7 +3814,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3844,12 +3824,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC</t>
+          <t>BLIL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SEDEMAC Mechatronics Limited</t>
+          <t>Balmer Lawrie Investments Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3863,63 +3843,61 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>13927</v>
+        <v>1596</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>116</v>
+        <v>8.91</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3152.9</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3152.9</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>59.08</v>
-      </c>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n">
-        <v>117.28</v>
+        <v>0.99</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>7.04</v>
+        <v>0.17</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>7.83</v>
+        <v>0.18</v>
       </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="2" t="n">
-        <v>110.2</v>
+        <v>0.8</v>
       </c>
       <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="n">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>104</v>
+        <v>278</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -3934,107 +3912,103 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>MBAPL</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Madhya Bharat Agro Products Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>DRAGARWQ</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Dr Agarwals Eye Hospital Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>7381</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
+      <c r="F34" s="3" t="n">
+        <v>2563</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J34" s="2" t="n">
-        <v>168.46</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>168.46</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>81.23999999999999</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>99.56999999999999</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="W34" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="X34" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="J34" s="3" t="n">
+        <v>5373.5</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>5395</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U34" s="3" t="n"/>
+      <c r="V34" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z34" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
+      <c r="AB34" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4046,12 +4020,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>SUNRAKSHAK</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
+          <t>Sunrakshakk Industries India Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4065,65 +4039,61 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>5895</v>
+        <v>1163</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>26.7</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>190.68</v>
+        <v>380.45</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>190.68</v>
+        <v>380.45</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>86.03</v>
-      </c>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n">
-        <v>75.11</v>
+        <v>0.93</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>4.03</v>
+        <v>0.17</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>4.42</v>
+        <v>0.18</v>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="U35" s="2" t="n"/>
       <c r="V35" s="2" t="n">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>8.9</v>
+        <v>22.9</v>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4138,7 +4108,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4148,17 +4118,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>ASHIKAG</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>Ashika Global Securities Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4167,61 +4137,57 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>5572</v>
+        <v>3208</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>25.4</v>
+        <v>42.7</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7749</v>
+        <v>436.3</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>7781</v>
+        <v>436.3</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>-0.41</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>84.89</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>50.78</v>
-      </c>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n">
-        <v>58.01</v>
+        <v>0.89</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>4.03</v>
+        <v>0.17</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>4.42</v>
+        <v>0.18</v>
       </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="2" t="n">
-        <v>54</v>
+        <v>0.7</v>
       </c>
       <c r="U36" s="2" t="n"/>
       <c r="V36" s="2" t="n">
-        <v>219</v>
+        <v>73</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>156</v>
+        <v>60</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>40.4</v>
+        <v>21.7</v>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
@@ -4240,7 +4206,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4216,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Vijaya Diagnostic Centre Limited</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4265,65 +4231,69 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1791</v>
+        <v>15046</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>58.7</v>
+        <v>80.3</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>588.4</v>
+        <v>1482.4</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>588.4</v>
+        <v>1510.6</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>79.5</v>
+        <v>15.9</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>49</v>
+        <v>48.06</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>140.29</v>
+        <v>45.13</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>4.03</v>
+        <v>1.99</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S37" s="2" t="n"/>
+        <v>2.41</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>11.27</v>
+      </c>
       <c r="T37" s="2" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="U37" s="2" t="n"/>
+        <v>43.1</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>33.9</v>
+      </c>
       <c r="V37" s="2" t="n">
-        <v>30.5</v>
+        <v>187</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>28.1</v>
+        <v>173</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
@@ -4342,417 +4312,421 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>ACCENTMIC</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>ACCENTMIC</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>583</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>583</v>
-      </c>
-      <c r="L38" s="2" t="n">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>S.J.S. Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>8166</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>2561.7</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>2561.7</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>32.12</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>81.14</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>100.58</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S38" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T38" s="2" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="U38" s="2" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="V38" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="W38" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="X38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S38" s="3" t="n"/>
+      <c r="T38" s="3" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="U38" s="3" t="n"/>
+      <c r="V38" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>KSHINTL</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>KSH International Limited</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>6969</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>1028.6</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>1028.6</v>
-      </c>
-      <c r="L39" s="2" t="n">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>AFCOM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Afcom Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>4680</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>1608.8</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>1608.8</v>
+      </c>
+      <c r="L39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>61.92</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>184.97</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>189.75</v>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>-1.26</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="U39" s="2" t="n"/>
-      <c r="V39" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="W39" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="X39" s="2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z39" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
+      <c r="AB39" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>SGMART</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>SG Mart Limited</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>MANINDS</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Man Industries (India) Limited</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>9274</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>735.85</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>747.15</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>75.66</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>105.49</v>
-      </c>
-      <c r="Q40" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="2" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="U40" s="2" t="n"/>
-      <c r="V40" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="W40" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="X40" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="n">
+        <v>5417</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>718.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>721.4</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S40" s="3" t="n"/>
+      <c r="T40" s="3" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="U40" s="3" t="n"/>
+      <c r="V40" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z40" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
+      <c r="AB40" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>COMSYN</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Commercial Syn Bags Limited</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Pricol Limited</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>1163</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>288.33</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>288.33</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Auto</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>9509</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>103.74</v>
-      </c>
-      <c r="Q41" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R41" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S41" s="2" t="n"/>
-      <c r="T41" s="2" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="U41" s="2" t="n"/>
-      <c r="V41" s="2" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="W41" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X41" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="I41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>790.9</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>806.55</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>77.41</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z41" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
+      <c r="AB41" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4764,12 +4738,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>Shukra Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4779,69 +4753,61 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>16077</v>
+        <v>1940</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>56.5</v>
+        <v>57.1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>822</v>
+        <v>44.07</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>822</v>
+        <v>44.31</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>71.81999999999999</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>151.53</v>
-      </c>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n">
-        <v>80.93000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>4.03</v>
+        <v>-0.35</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>12.7</v>
-      </c>
+        <v>-0.29</v>
+      </c>
+      <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>68.2</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="U42" s="2" t="n"/>
       <c r="V42" s="2" t="n">
-        <v>298</v>
+        <v>33</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>244</v>
+        <v>28</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>22.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
@@ -4860,1032 +4826,940 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>KDDL</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>KDDL Limited</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>RPEL</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Limited</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>4834</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>3930.2</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>3945.9</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="n">
+        <v>7451</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="W43" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="X43" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="I43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>1662.4</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>1689.8</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>126.43</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>179.2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="Z43" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
+      <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
+      <c r="AB43" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>DRAGARWQ</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>MARINE</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Marine Electricals (India) Limited</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>2611</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
+      <c r="F44" s="3" t="n">
+        <v>5350</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="J44" s="2" t="n">
-        <v>5403</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>5418</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="W44" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
+      <c r="J44" s="3" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>102.09</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
+      <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
+      <c r="AB44" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>PGIL</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Pearl Global Industries Limited</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>11430</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>2474.6</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>2480.4</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2402</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>56.02</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S45" s="2" t="n"/>
-      <c r="T45" s="2" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="n">
-        <v>304</v>
-      </c>
-      <c r="W45" s="2" t="n">
-        <v>271</v>
-      </c>
-      <c r="X45" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
+      <c r="I45" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>1058.9</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1058.9</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>165.99</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z45" s="2" t="inlineStr">
+      <c r="Z45" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
+      <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
+      <c r="AB45" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SUDEEPPHRM</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Sudeep Pharma Limited</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>RAMRAT</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Ram Ratna Wires Limited</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Chemicals</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>12487</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>1105.55</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>1108.4</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>70.36</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>42.81</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="S46" s="2" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="U46" s="2" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="V46" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="W46" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="X46" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>4537</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>485.85</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="Z46" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
+      <c r="AB46" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>HAPPYFORGE</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Happy Forgings Limited</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>19721</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>2089.6</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>2089.6</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S47" s="2" t="n"/>
-      <c r="T47" s="2" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="W47" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="X47" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="Y47" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="n">
+        <v>6169</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>199.68</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>200.39</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>49.01</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S47" s="3" t="n"/>
+      <c r="T47" s="3" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="U47" s="3" t="n"/>
+      <c r="V47" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA47" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
+      <c r="AB47" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Rajputana Stainless Limited</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SGMART</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>SG Mart Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>1382</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>165.42</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>166.77</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="S48" s="2" t="n"/>
-      <c r="T48" s="2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="n">
+        <v>10278</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>811.55</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>820.35</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>126.62</v>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S48" s="3" t="n"/>
+      <c r="T48" s="3" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="U48" s="3" t="n"/>
+      <c r="V48" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA48" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB48" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>GSPCROP</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>GSP Crop Science Limited</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Shilpa Medicare Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>2774</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>596.25</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>597.5</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S49" s="2" t="n"/>
-      <c r="T49" s="2" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="U49" s="2" t="n"/>
-      <c r="V49" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="W49" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="X49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>16468</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>855.8</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>855.8</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>162.61</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z49" s="2" t="inlineStr">
+      <c r="Z49" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
+      <c r="AA49" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
+      <c r="AB49" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSHBULL</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>1908</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Rajputana Stainless Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1409</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>166.99</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>168.01</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>27.52</v>
+      </c>
+      <c r="O50" s="3" t="n"/>
+      <c r="P50" s="3" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="U50" s="3" t="n"/>
+      <c r="V50" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X50" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J50" s="2" t="n">
-        <v>1245.9</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>1247.65</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="O50" s="2" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>32.63</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S50" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="T50" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="U50" s="2" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="V50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr">
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>NGLFINE</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>NGL Fine-Chem Limited</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>2135</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>3454</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>3457.8</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>51.66</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>151.53</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="S51" s="2" t="n"/>
-      <c r="T51" s="2" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="U51" s="2" t="n"/>
-      <c r="V51" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="W51" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="X51" s="2" t="n">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>1266.9</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z51" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>INVPRECQ</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Investment &amp; Precision Castings Limited</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>1217</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>1217.3</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>1217.3</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>98.05</v>
-      </c>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n">
-        <v>81.12</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="2" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="W52" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="X52" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y52" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z52" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr">
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB52"/>
+  <autoFilter ref="A1:AB51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5904,80 +5778,80 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>ATH Radar - weekly screen</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr"/>
+      <c r="B1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Run date</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-15 (prices as of 2026-08-14)</t>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-25 (prices as of 2026-08-24)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Universe</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2378 NSE mainboard (EQ) + 1014 NSE Emerge SME</t>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2529 NSE mainboard (EQ) + 1025 NSE Emerge SME</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Filters</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Within 2% of all-time-high close; TTM return above Nifty 500, Nifty Total Market, sector index (mainboard) / NIFTY SME EMERGE (SME); TTM PAT &gt;= every prior annual and rolling window (screener.in); mcap Rs 1,000-20,000 Cr</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Sort</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Newest entrant into the 2% ATH zone first; green rows new since previous run</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>3392 screened -&gt; 172 at ATH -&gt; 169 outperforming -&gt; 103 record PAT -&gt; 51 in mcap band</t>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3554 screened -&gt; 244 at ATH -&gt; 225 outperforming -&gt; 112 record PAT -&gt; 50 in mcap band</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Caveats</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>SME price history since Jul-2024, unadjusted for corporate actions; PAT history limited to screener-visible years; mainboard prices split-adjusted (Yahoo). Factual screen - not investment advice</t>
         </is>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,8 +84,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5821</v>
+        <v>5839</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>4.84</v>
+        <v>5.06</v>
       </c>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n">
-        <v>17.74</v>
+        <v>17.73</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>3.07</v>
@@ -726,111 +726,111 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>OBSCP</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>OBSCP</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SME-NSE</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>2249</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>2287</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="2" t="n">
         <v>854.8</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>860.15</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="N3" s="2" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="O3" s="2" t="n">
         <v>175.61</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="2" t="n">
         <v>165.63</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>2.26</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="2" t="n">
         <v>2.66</v>
       </c>
-      <c r="S3" s="3" t="n">
+      <c r="S3" s="2" t="n">
         <v>-4.34</v>
       </c>
-      <c r="T3" s="3" t="n">
+      <c r="T3" s="2" t="n">
         <v>163.4</v>
       </c>
-      <c r="U3" s="3" t="n">
+      <c r="U3" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" s="2" t="n">
         <v>31.5</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="W3" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="X3" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -842,12 +842,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Shadowfax Technologies Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>15180</v>
+        <v>1986</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>89.7</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -875,51 +875,51 @@
         <v>2</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>260.34</v>
+        <v>1963.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>264.84</v>
+        <v>1984.5</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.06</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>30.37</v>
+        <v>75.81</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>122.63</v>
+        <v>116.81</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>136.71</v>
+        <v>140.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n">
-        <v>134.8</v>
+        <v>138.5</v>
       </c>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n">
-        <v>169</v>
+        <v>38.9</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>50.9</v>
+        <v>14.4</v>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
@@ -934,319 +934,315 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>KTKBANK</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>The Karnataka Bank Limited</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SHADOWFAX</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Financial Services</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>12611</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>15104</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="3" t="n">
-        <v>333.25</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>335.05</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>24.72</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>64.45</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>93.81999999999999</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>1437</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>1341</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="J5" s="2" t="n">
+        <v>260.34</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>264.84</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>136.72</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="U5" s="2" t="n"/>
+      <c r="V5" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z5" s="3" t="inlineStr">
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Standard Engineering Technology Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The Karnataka Bank Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>6136</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>12692</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>127.12</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>147.88</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>71.17</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+      <c r="J6" s="2" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>335.6</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>65.39</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>93.81</v>
+      </c>
+      <c r="Q6" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="S6" s="2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>CFF</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>CFF FLUID CONTROL LIMITED</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>2199</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Standard Engineering Technology Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>1041.85</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>1041.85</v>
-      </c>
-      <c r="L7" s="3" t="n">
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>312.35</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>38.19</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>92.22</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>61.77</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr">
+      <c r="N7" s="2" t="n">
+        <v>130.15</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>151.19</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="U7" s="2" t="n"/>
+      <c r="V7" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1258,29 +1254,29 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>CFF</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
+          <t>CFF FLUID CONTROL LIMITED</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>8921</v>
+        <v>2225</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>49.2</v>
+        <v>56.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1288,73 +1284,73 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>907.55</v>
+        <v>1041.85</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>925.15</v>
+        <v>1041.85</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>13.33</v>
+        <v>38.19</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>31.39</v>
+        <v>92.22</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>28.42</v>
+        <v>61.77</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>11.27</v>
+        <v>-4.34</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>26.4</v>
+        <v>59.5</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>17.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>174</v>
+        <v>39</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>171</v>
+        <v>39</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1383,10 +1379,10 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2116</v>
+        <v>2097</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>33</v>
+        <v>32.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1452,107 +1448,107 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>KMEW</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Knowledge Marine &amp; Engineering Works Limited</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>6793</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="n">
+        <v>6820</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="2" t="n">
         <v>2712.7</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>2756.5</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="2" t="n">
         <v>-1.59</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>24.76</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>70.92</v>
-      </c>
-      <c r="P10" s="3" t="n">
+      <c r="N10" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>71.52</v>
+      </c>
+      <c r="P10" s="2" t="n">
         <v>184.11</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n">
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n">
         <v>182.1</v>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n">
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1583,10 +1579,10 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6644</v>
+        <v>6550</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1611,10 +1607,10 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>24.47</v>
+        <v>22.83</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>129.55</v>
+        <v>126.53</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>180.64</v>
@@ -1656,7 +1652,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1681,10 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1486</v>
+        <v>1505</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>69</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1762,7 +1758,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4057</v>
+        <v>4024</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40.8</v>
+        <v>40.5</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1819,10 +1815,10 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>49.07</v>
+        <v>47.97</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>152.51</v>
+        <v>150.64</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>110.8</v>
@@ -1864,7 +1860,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1889,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5638</v>
+        <v>5642</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46.1</v>
@@ -1966,107 +1962,107 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>MBAPL</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Madhya Bharat Agro Products Limited</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>7479</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>7455</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="2" t="n">
         <v>168.91</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>170.69</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>170.33</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>84.09</v>
-      </c>
-      <c r="P15" s="3" t="n">
+      <c r="N15" s="2" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>94.98</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n">
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n">
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2097,7 +2093,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1852</v>
+        <v>1859</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>122</v>
@@ -2125,10 +2121,10 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>81.11</v>
+        <v>83.02</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>123.09</v>
+        <v>125.44</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>64.23</v>
@@ -2168,7 +2164,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -2274,7 +2270,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2303,10 +2299,10 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2018</v>
+        <v>1990</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -2380,7 +2376,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2409,10 +2405,10 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4303</v>
+        <v>4279</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2437,10 +2433,10 @@
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>7.04</v>
+        <v>6.34</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>24.46</v>
+        <v>23.65</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>24.19</v>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2507,10 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2074</v>
+        <v>2042</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2528,21 +2524,21 @@
         <v>270.52</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>270.9</v>
+        <v>270.52</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>21.97</v>
+        <v>19.63</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>25.74</v>
+        <v>23.32</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>17.89</v>
@@ -2584,7 +2580,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2609,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4233</v>
+        <v>4230</v>
       </c>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
@@ -2678,7 +2674,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2784,107 +2780,107 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>COMSYN</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>1169</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J23" s="2" t="n">
         <v>289.17</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="2" t="n">
         <v>289.77</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="2" t="n">
         <v>-0.21</v>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="N23" s="3" t="n">
-        <v>86.53</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="P23" s="3" t="n">
+      <c r="N23" s="2" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>51.05</v>
+      </c>
+      <c r="P23" s="2" t="n">
         <v>109.39</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n">
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n">
         <v>107.4</v>
       </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n">
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n">
         <v>29.7</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="X23" s="3" t="n">
+      <c r="X23" s="2" t="n">
         <v>6.1</v>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z23" s="3" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2915,10 +2911,10 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1594</v>
+        <v>1571</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>32.6</v>
+        <v>32.1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2943,10 +2939,10 @@
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>49.36</v>
+        <v>47.23</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>104.43</v>
+        <v>101.51</v>
       </c>
       <c r="P24" s="2" t="n">
         <v>96.15000000000001</v>
@@ -2988,7 +2984,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3017,10 +3013,10 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1945</v>
+        <v>1931</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -3041,17 +3037,17 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>54.38</v>
+        <v>53.49</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>69.47</v>
+        <v>68.5</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>79.27</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>1.99</v>
@@ -3090,7 +3086,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3119,10 +3115,10 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>5983</v>
+        <v>6057</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -3136,18 +3132,18 @@
         <v>595.25</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>599.95</v>
+        <v>600</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>58.42</v>
+        <v>60.17</v>
       </c>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n">
@@ -3190,7 +3186,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3219,10 +3215,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>9130</v>
+        <v>9051</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>78</v>
+        <v>77.3</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -3247,13 +3243,13 @@
         </is>
       </c>
       <c r="N27" s="2" t="n">
-        <v>35</v>
+        <v>33.99</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>67.43000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>70.92</v>
+        <v>70.91</v>
       </c>
       <c r="Q27" s="2" t="n">
         <v>25.87</v>
@@ -3292,7 +3288,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3298,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Gokul Agro Resources Limited</t>
+          <t>Canara HSBC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3317,14 +3313,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Nifty FMCG</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7318</v>
+        <v>14540</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>17.4</v>
+        <v>111</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -3332,58 +3328,58 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>244.05</v>
+        <v>154.7</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>248.78</v>
+        <v>155.24</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-1.9</v>
+        <v>-0.35</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N28" s="2" t="n">
-        <v>8.5</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>43.61</v>
+        <v>2.38</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>48.4</v>
+        <v>38.85</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>1.99</v>
+        <v>-0.37</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>2.41</v>
+        <v>0.17</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>-14.64</v>
+        <v>-5.01</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>46.4</v>
+        <v>39.2</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>63</v>
+        <v>43.9</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>421</v>
+        <v>132</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>370</v>
+        <v>127</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>13.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3398,7 +3394,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3408,84 +3404,84 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>ZELIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Canara HSBC Life Insurance Company Limited</t>
+          <t>Zelio E Mobility Limited</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>14620</v>
+        <v>1905</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>154.7</v>
+        <v>882.95</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>155.24</v>
+        <v>882.95</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N29" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>2.75</v>
+        <v>238.49</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>38.84</v>
+        <v>443.02</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>-0.37</v>
+        <v>1.74</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.17</v>
+        <v>2.21</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>-5.01</v>
+        <v>-4.4</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>39.2</v>
+        <v>441.3</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>43.9</v>
+        <v>447.4</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
@@ -3494,17 +3490,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3514,29 +3510,29 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ZELIO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Zelio E Mobility Limited</t>
+          <t>CORONA Remedies Limited</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1867</v>
+        <v>12914</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>60.9</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -3547,174 +3543,166 @@
         <v>5</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>882.95</v>
+        <v>2149</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>882.95</v>
+        <v>2165.8</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>-0.78</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="N30" s="2" t="n">
-        <v>83.91</v>
+        <v>24.41</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>238.49</v>
+        <v>32.39</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>443.02</v>
+        <v>49.4</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>1.74</v>
+        <v>-0.9</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>2.21</v>
+        <v>-0.21</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>-4.4</v>
+        <v>11.6</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>441.3</v>
+        <v>50.3</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>447.4</v>
+        <v>37.8</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>CORONA</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>CORONA Remedies Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ONEGLOBAL</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>One Global Service Provider Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>13109</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>2149</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>2165.8</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="J31" s="2" t="n">
+        <v>553.95</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>564.1</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>198</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA31" s="3" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
+      <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3726,12 +3714,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ONEGLOBAL</t>
+          <t>BLIL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>One Global Service Provider Limited</t>
+          <t>Balmer Lawrie Investments Limited</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3745,10 +3733,10 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1077</v>
+        <v>1598</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.6</v>
+        <v>8.92</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -3756,26 +3744,26 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>553.95</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>564.1</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n">
-        <v>3.14</v>
+        <v>0.99</v>
       </c>
       <c r="Q32" s="2" t="n">
         <v>0.17</v>
@@ -3785,21 +3773,21 @@
       </c>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="2" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="U32" s="2" t="n"/>
       <c r="V32" s="2" t="n">
-        <v>74</v>
+        <v>282</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -3814,7 +3802,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3812,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BLIL</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Balmer Lawrie Investments Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3843,10 +3831,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1596</v>
+        <v>2574</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>8.91</v>
+        <v>33.8</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -3854,26 +3842,26 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>72.01000000000001</v>
+        <v>5373.5</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>72.01000000000001</v>
+        <v>5395</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="Q33" s="2" t="n">
         <v>0.17</v>
@@ -3887,17 +3875,17 @@
       </c>
       <c r="U33" s="2" t="n"/>
       <c r="V33" s="2" t="n">
-        <v>282</v>
+        <v>75</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>278</v>
+        <v>70</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -3912,103 +3900,103 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>DRAGARWQ</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SUNRAKSHAK</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Sunrakshakk Industries India Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>2563</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="n">
+        <v>1163</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>5373.5</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>5395</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="J34" s="2" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Q34" s="3" t="n">
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Q34" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n">
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n">
         <v>0.8</v>
       </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA34" s="3" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB34" s="3" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4020,17 +4008,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SUNRAKSHAK</t>
+          <t>ASHIKAG</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Sunrakshakk Industries India Limited</t>
+          <t>Ashika Global Securities Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4039,10 +4027,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1163</v>
+        <v>3175</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>26.7</v>
+        <v>42.3</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -4053,10 +4041,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>380.45</v>
+        <v>436.3</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>380.45</v>
+        <v>436.3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -4069,7 +4057,7 @@
       <c r="N35" s="2" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="Q35" s="2" t="n">
         <v>0.17</v>
@@ -4079,17 +4067,17 @@
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="U35" s="2" t="n"/>
       <c r="V35" s="2" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
@@ -4108,7 +4096,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4118,76 +4106,84 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ASHIKAG</t>
+          <t>VIJAYA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Ashika Global Securities Limited</t>
+          <t>Vijaya Diagnostic Centre Limited</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>3208</v>
+        <v>14995</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>42.7</v>
+        <v>80</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>436.3</v>
+        <v>1482.4</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>436.3</v>
+        <v>1510.6</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>47.74</v>
+      </c>
       <c r="P36" s="2" t="n">
-        <v>0.89</v>
+        <v>45.14</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>0.17</v>
+        <v>1.99</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S36" s="2" t="n"/>
+        <v>2.41</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>11.27</v>
+      </c>
       <c r="T36" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U36" s="2" t="n"/>
+        <v>43.1</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>33.9</v>
+      </c>
       <c r="V36" s="2" t="n">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>21.7</v>
+        <v>8.1</v>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
@@ -4206,7 +4202,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4216,12 +4212,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>SJS</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Limited</t>
+          <t>S.J.S. Enterprises Limited</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4231,45 +4227,45 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>15046</v>
+        <v>8152</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>80.3</v>
+        <v>42.8</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1482.4</v>
+        <v>2561.7</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1510.6</v>
+        <v>2561.7</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-1.87</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N37" s="2" t="n">
-        <v>15.9</v>
+        <v>24.77</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>48.06</v>
+        <v>37.78</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>45.13</v>
+        <v>90.28</v>
       </c>
       <c r="Q37" s="2" t="n">
         <v>1.99</v>
@@ -4277,23 +4273,19 @@
       <c r="R37" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S37" s="2" t="n">
-        <v>11.27</v>
-      </c>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="U37" s="2" t="n">
-        <v>33.9</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="U37" s="2" t="n"/>
       <c r="V37" s="2" t="n">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>8.1</v>
+        <v>22.7</v>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
@@ -4312,421 +4304,417 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>SJS</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>S.J.S. Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>8166</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AFCOM</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Afcom Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>4608</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>2561.7</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>2561.7</v>
-      </c>
-      <c r="L38" s="3" t="n">
+      <c r="J38" s="2" t="n">
+        <v>1608.8</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1608.8</v>
+      </c>
+      <c r="L38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>25.08</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>38.11</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>90.28</v>
-      </c>
-      <c r="Q38" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" s="3" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="U38" s="3" t="n"/>
-      <c r="V38" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>172</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>83.56999999999999</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA38" s="3" t="inlineStr">
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB38" s="3" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>AFCOM</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Afcom Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>4680</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>MANINDS</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Man Industries (India) Limited</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>5461</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="3" t="n">
-        <v>1608.8</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>1608.8</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>70.20999999999999</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>86.69</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>83.56999999999999</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
+      <c r="J39" s="2" t="n">
+        <v>718.1</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>728.5</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="U39" s="2" t="n"/>
+      <c r="V39" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA39" s="3" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB39" s="3" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>MANINDS</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Limited</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>PRICOLLTD</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Pricol Limited</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>5417</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Auto</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>9580</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>718.1</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>721.4</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>31.77</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>68.79000000000001</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>82.05</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+      <c r="I40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>790.9</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>806.55</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>27.02</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>77.41</v>
+      </c>
+      <c r="Q40" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y40" s="3" t="inlineStr">
+      <c r="S40" s="2" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z40" s="3" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA40" s="3" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB40" s="3" t="inlineStr">
+      <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>PRICOLLTD</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Pricol Limited</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Auto</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>9509</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>1948</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>790.9</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>806.55</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>38.93</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>26.17</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>77.41</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="X41" s="3" t="n">
+      <c r="I41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="n">
         <v>6.8</v>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
+      <c r="U41" s="2" t="n"/>
+      <c r="V41" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z41" s="3" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA41" s="3" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB41" s="3" t="inlineStr">
+      <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4738,12 +4726,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4757,57 +4745,61 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1940</v>
+        <v>7503</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>57.1</v>
+        <v>120</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>44.07</v>
+        <v>1662.4</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>44.31</v>
+        <v>1689.8</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-0.54</v>
+        <v>-1.62</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>127.92</v>
+      </c>
       <c r="P42" s="2" t="n">
-        <v>6.4</v>
+        <v>179.21</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>-0.35</v>
+        <v>1.99</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>-0.29</v>
+        <v>2.41</v>
       </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="2" t="n">
-        <v>6.8</v>
+        <v>177.2</v>
       </c>
       <c r="U42" s="2" t="n"/>
       <c r="V42" s="2" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>17.9</v>
+        <v>14.5</v>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
@@ -4826,940 +4818,736 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>RPEL</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Limited</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>MARINE</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Marine Electricals (India) Limited</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>7451</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="F43" s="2" t="n">
+        <v>5347</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>1662.4</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>1689.8</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>126.43</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>179.2</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+      <c r="I43" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>56.01</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>122.72</v>
+      </c>
+      <c r="Q43" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="U43" s="2" t="n"/>
+      <c r="V43" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z43" s="3" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA43" s="3" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB43" s="3" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>MARINE</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Marine Electricals (India) Limited</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>5350</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>2389</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J44" s="3" t="n">
-        <v>382.9</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>382.9</v>
-      </c>
-      <c r="L44" s="3" t="n">
+      <c r="J44" s="2" t="n">
+        <v>1058.9</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1058.9</v>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="N44" s="3" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>102.09</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>122.72</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
+      <c r="N44" s="2" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>165.99</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z44" s="3" t="inlineStr">
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA44" s="3" t="inlineStr">
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB44" s="3" t="inlineStr">
+      <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>2402</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>RAMRAT</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Ram Ratna Wires Limited</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>4529</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>1058.9</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>1058.9</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>87.81</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>165.99</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
+      <c r="J45" s="2" t="n">
+        <v>485.85</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>487</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U45" s="2" t="n"/>
+      <c r="V45" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z45" s="3" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA45" s="3" t="inlineStr">
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB45" s="3" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>RAMRAT</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Ram Ratna Wires Limited</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>4537</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>485.85</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>486.5</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>51.52</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>42.53</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+      <c r="F46" s="2" t="n">
+        <v>6113</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>199.68</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>199.68</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>98.11</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>67.65000000000001</v>
+      </c>
+      <c r="Q46" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="U46" s="2" t="n"/>
+      <c r="V46" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA46" s="3" t="inlineStr">
+      <c r="AA46" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB46" s="3" t="inlineStr">
+      <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>KRISHANA</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Krishana Phoschem Limited</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Shilpa Medicare Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>6169</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>199.68</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>200.39</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="M47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N47" s="3" t="n">
-        <v>49.01</v>
-      </c>
-      <c r="O47" s="3" t="n">
-        <v>100.85</v>
-      </c>
-      <c r="P47" s="3" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="Q47" s="3" t="n">
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>16546</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>855.8</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>855.8</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>164.31</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="Q47" s="2" t="n">
         <v>1.99</v>
       </c>
-      <c r="R47" s="3" t="n">
+      <c r="R47" s="2" t="n">
         <v>2.41</v>
       </c>
-      <c r="S47" s="3" t="n"/>
-      <c r="T47" s="3" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="U47" s="3" t="n"/>
-      <c r="V47" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="W47" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="X47" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z47" s="3" t="inlineStr">
+      <c r="S47" s="2" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA47" s="3" t="inlineStr">
+      <c r="AA47" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB47" s="3" t="inlineStr">
+      <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>SGMART</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>SG Mart Limited</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Rajputana Stainless Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>10278</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>811.55</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>820.35</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="M48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N48" s="3" t="n">
-        <v>35.05</v>
-      </c>
-      <c r="O48" s="3" t="n">
-        <v>89.41</v>
-      </c>
-      <c r="P48" s="3" t="n">
-        <v>126.62</v>
-      </c>
-      <c r="Q48" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R48" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S48" s="3" t="n"/>
-      <c r="T48" s="3" t="n">
-        <v>125.2</v>
-      </c>
-      <c r="U48" s="3" t="n"/>
-      <c r="V48" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="W48" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="X48" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
+      <c r="F48" s="2" t="n">
+        <v>1396</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>166.99</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>166.99</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>26.53</v>
+      </c>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="U48" s="2" t="n"/>
+      <c r="V48" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA48" s="3" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB48" s="3" t="inlineStr">
+      <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>SHILPAMED</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Shilpa Medicare Limited</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>16468</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>855.8</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>855.8</v>
-      </c>
-      <c r="L49" s="3" t="n">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>1943</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1266.9</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1270.2</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>-4.34</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="X49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N49" s="3" t="n">
-        <v>66.73999999999999</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>162.61</v>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>101.59</v>
-      </c>
-      <c r="Q49" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R49" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S49" s="3" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="T49" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="U49" s="3" t="n">
-        <v>90.3</v>
-      </c>
-      <c r="V49" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="W49" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="X49" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z49" s="3" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA49" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB49" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Rajputana Stainless Limited</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1409</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>166.99</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>168.01</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="M50" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N50" s="3" t="n">
-        <v>27.52</v>
-      </c>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="3" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="Q50" s="3" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="R50" s="3" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="S50" s="3" t="n"/>
-      <c r="T50" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="U50" s="3" t="n"/>
-      <c r="V50" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="W50" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X50" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y50" s="3" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z50" s="3" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA50" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB50" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>AAYUSHBULL</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1944</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>1266.9</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>1270.2</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="P51" s="3" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="Q51" s="3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R51" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S51" s="3" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T51" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="W51" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="X51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z51" s="3" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA51" s="3" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB51" s="3" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB51"/>
+  <autoFilter ref="A1:AB49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5841,7 +5629,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3554 screened -&gt; 244 at ATH -&gt; 225 outperforming -&gt; 112 record PAT -&gt; 50 in mcap band</t>
+          <t>3554 screened -&gt; 251 at ATH -&gt; 229 outperforming -&gt; 111 record PAT -&gt; 48 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB49"/>
+  <dimension ref="A1:AB55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,78 +636,84 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>NIRLON</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nirlon Limited</t>
+          <t>OBSCP</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5839</v>
+        <v>2238</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16.4</v>
+        <v>71.2</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>642.1</v>
+        <v>866.05</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>647.95</v>
+        <v>873.3</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.83</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="O2" s="2" t="n"/>
+        <v>88.33</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>183.21</v>
+      </c>
       <c r="P2" s="2" t="n">
-        <v>17.73</v>
+        <v>181.14</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>3.07</v>
+        <v>4.38</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="S2" s="2" t="n"/>
+        <v>4.82</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>-2.19</v>
+      </c>
       <c r="T2" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="U2" s="2" t="n"/>
+        <v>176.8</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>183.3</v>
+      </c>
       <c r="V2" s="2" t="n">
-        <v>357</v>
+        <v>31.5</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>346</v>
+        <v>27</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>3.2</v>
+        <v>16.7</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -731,108 +737,108 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>OBSCP</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>OBSCP</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ACCENTMIC</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ACCENTMIC</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>SME-NSE</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>2287</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="F3" s="3" t="n">
+        <v>1453</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>854.8</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>860.15</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>81.76000000000001</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>175.61</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>165.63</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>163.4</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="n">
+        <v>605.85</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>605.85</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -842,94 +848,98 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>YASHHV</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>Yash Highvoltage Limited</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1986</v>
+        <v>2947</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>51</v>
+        <v>75.7</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1963.4</v>
+        <v>986.1</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1984.5</v>
+        <v>1003.7</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.75</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>75.81</v>
+        <v>36.38</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>116.81</v>
+        <v>115.09</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>140.5</v>
+        <v>106.41</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.99</v>
+        <v>4.38</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S4" s="3" t="n"/>
+        <v>4.82</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-2.19</v>
+      </c>
       <c r="T4" s="3" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="U4" s="3" t="n"/>
+        <v>102</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>108.6</v>
+      </c>
       <c r="V4" s="3" t="n">
-        <v>38.9</v>
+        <v>38</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>14.4</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
@@ -944,94 +954,98 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SHADOWFAX</t>
+          <t>CFF</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Shadowfax Technologies Limited</t>
+          <t>CFF FLUID CONTROL LIMITED</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15104</v>
+        <v>2175</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>89.3</v>
+        <v>55.5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>260.34</v>
+        <v>1037.05</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>264.84</v>
+        <v>1046.1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-1.7</v>
+        <v>-0.87</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>29.6</v>
+        <v>44.02</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>121.3</v>
+        <v>95.08</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>136.72</v>
+        <v>63.1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1.86</v>
+        <v>4.38</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="S5" s="2" t="n"/>
+        <v>4.82</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>-2.19</v>
+      </c>
       <c r="T5" s="2" t="n">
-        <v>134.9</v>
-      </c>
-      <c r="U5" s="2" t="n"/>
+        <v>58.7</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>65.3</v>
+      </c>
       <c r="V5" s="2" t="n">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>50.9</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1046,12 +1060,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The Karnataka Bank Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1061,73 +1075,69 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>12692</v>
+        <v>2008</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.880000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>333.25</v>
+        <v>2007.1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>335.6</v>
+        <v>2007.1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>25.43</v>
+        <v>77.02</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>65.39</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>93.81</v>
+        <v>145.79</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
+        <v>3.78</v>
+      </c>
+      <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>94.40000000000001</v>
-      </c>
+        <v>142.4</v>
+      </c>
+      <c r="U6" s="2" t="n"/>
       <c r="V6" s="2" t="n">
-        <v>1437</v>
+        <v>38.9</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1341</v>
+        <v>34</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1147,104 +1157,104 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Standard Engineering Technology Limited</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>CNL</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Creative Newtech Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>6201</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>312.35</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>130.15</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>151.19</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>71.17</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="n">
+        <v>1865</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1242.15</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1264.15</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>91.94</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>87.26000000000001</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>96.98</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1254,98 +1264,94 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CFF</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>CFF FLUID CONTROL LIMITED</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2225</v>
+        <v>5762</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>56.8</v>
+        <v>28.2</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1041.85</v>
+        <v>768.2</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1041.85</v>
+        <v>768.2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>38.19</v>
+        <v>45.19</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>92.22</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>61.77</v>
+        <v>96.59</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>2.26</v>
+        <v>3.34</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>-4.34</v>
-      </c>
+        <v>3.78</v>
+      </c>
+      <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>66.09999999999999</v>
-      </c>
+        <v>93.2</v>
+      </c>
+      <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>39</v>
+        <v>188</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1355,716 +1361,720 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>BLUECLOUDS</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Blue Cloud Softech Solutions Limited</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>AZAD</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Azad Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>2097</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="n">
+        <v>18409</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>2850.5</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>2899.9</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>36.23</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>85.73999999999999</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KMEW</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>QPOWER</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Quality Power Electrical Equipments Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>6820</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>2712.7</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>2756.5</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>71.52</v>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>184.11</v>
-      </c>
-      <c r="Q10" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="W10" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="X10" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="n">
+        <v>11084</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1431.2</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1431.2</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Z10" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Industries Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>SEAMECLTD</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Seamec Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>6550</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>504.25</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>510.9</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>126.53</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>180.64</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n">
-        <v>178.6</v>
-      </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="W11" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="n">
+        <v>4263</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1676.6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1699</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SHREEREF</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>SHREE REFRIGERATIONS LIMITED</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1505</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>399.65</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>405.4</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>67.70999999999999</v>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>118.93</v>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>121.78</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="X12" s="2" t="n">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>VADILALIND</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Vadilal Industries Limited</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5680</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>66.66</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>INDOTECH</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Indo Tech Transformers Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Sudeep Pharma Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>4024</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>3850.6</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>3902.5</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>-1.33</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>150.64</v>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n">
-        <v>108.8</v>
-      </c>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="W13" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Chemicals</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>13013</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1152.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>1156.4</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>68.09</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>FCL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Fineotex Chemical Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>MMP</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>MMP Industries Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>5642</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>99.55</v>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>97.18000000000001</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="W14" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="X14" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="n">
+        <v>1027</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>404.4</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>412.35</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>44.47</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>MBAPL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Madhya Bharat Agro Products Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>VINCOFE</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Vintage Coffee And Beverages Limited</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
-        <v>7455</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>168.91</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>170.33</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>55.28</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>94.98</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="n">
+        <v>2593</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>177.97</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>177.97</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2084,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING</t>
+          <t>TURTLEMINT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Limited</t>
+          <t>Turtlemint Fintech Solutions Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2093,58 +2103,52 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1859</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>122</v>
-      </c>
+        <v>4495</v>
+      </c>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>133.01</v>
+        <v>152.65</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>133.01</v>
+        <v>153.64</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>83.02</v>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>125.44</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n">
-        <v>64.23</v>
+        <v>12.77</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n">
-        <v>62.2</v>
+        <v>10.5</v>
       </c>
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n">
-        <v>-17.5</v>
+        <v>-144</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>-23</v>
+        <v>-145</v>
       </c>
       <c r="X16" s="2" t="n"/>
       <c r="Y16" s="2" t="inlineStr">
@@ -2169,108 +2173,104 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>AIRFLOA</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>1038</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Bliss GVS Pharma Limited</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6250</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="2" t="n">
-        <v>434</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>434</v>
-      </c>
-      <c r="L17" s="2" t="n">
+      <c r="J17" s="3" t="n">
+        <v>588.1</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>588.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>37.62</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>55.39</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="S17" s="2" t="n">
-        <v>-6.03</v>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="V17" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="W17" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="X17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>157.67</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>261.24</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2280,98 +2280,94 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VINYAS</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VINYAS</t>
+          <t>Knowledge Marine &amp; Engineering Works Limited</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1990</v>
+        <v>7741</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>64.5</v>
+        <v>59.7</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1603.15</v>
+        <v>3051.9</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1611.8</v>
+        <v>3051.9</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>51.96</v>
+        <v>44.82</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>62.26</v>
+        <v>82.11</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>32.77</v>
+        <v>214.97</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>2.26</v>
+        <v>3.34</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <v>-4.34</v>
-      </c>
+        <v>3.78</v>
+      </c>
+      <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>37.1</v>
-      </c>
+        <v>211.6</v>
+      </c>
+      <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2386,12 +2382,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VISHNU</t>
+          <t>AEROFLEX</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Vishnu Chemicals Limited</t>
+          <t>Aeroflex Industries Limited</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2405,61 +2401,61 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4279</v>
+        <v>7174</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>28.6</v>
+        <v>107</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>637.7</v>
+        <v>542.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>640.45</v>
+        <v>542.1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-0.43</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="N19" s="2" t="n">
-        <v>6.34</v>
+        <v>28.15</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>23.65</v>
+        <v>127.67</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>24.19</v>
+        <v>207.89</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="2" t="n">
-        <v>22.2</v>
+        <v>204.5</v>
       </c>
       <c r="U19" s="2" t="n"/>
       <c r="V19" s="2" t="n">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>5.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
@@ -2488,12 +2484,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2507,65 +2503,65 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2042</v>
+        <v>8029</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>10.9</v>
+        <v>128</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>270.52</v>
+        <v>1748.4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>270.52</v>
+        <v>1748.4</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N20" s="2" t="n">
-        <v>19.63</v>
+        <v>80.66</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>23.32</v>
+        <v>143.72</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>17.89</v>
+        <v>204.52</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="2" t="n">
-        <v>15.9</v>
+        <v>201.2</v>
       </c>
       <c r="U20" s="2" t="n"/>
       <c r="V20" s="2" t="n">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2585,96 +2581,104 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>TURTLEMINT</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Turtlemint Fintech Solutions Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
-        <v>4230</v>
-      </c>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
+      <c r="F21" s="3" t="n">
+        <v>14910</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="2" t="n">
-        <v>147.89</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>150.15</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S21" s="2" t="n"/>
-      <c r="T21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U21" s="2" t="n"/>
-      <c r="V21" s="2" t="n">
-        <v>-144</v>
-      </c>
-      <c r="W21" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="X21" s="2" t="n"/>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="J21" s="3" t="n">
+        <v>2231.7</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>2256.6</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>120.26</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>164.51</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n">
+        <v>161.2</v>
+      </c>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2684,43 +2688,43 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>MARINE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PRIZOR</t>
+          <t>Marine Electricals (India) Limited</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1157</v>
+        <v>5693</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>55.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1020.3</v>
+        <v>406.8</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1020.3</v>
+        <v>406.8</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -2731,51 +2735,47 @@
         </is>
       </c>
       <c r="N22" s="2" t="n">
-        <v>57.38</v>
+        <v>50.9</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>229.13</v>
+        <v>95.63</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>261.68</v>
+        <v>141.51</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>2.26</v>
+        <v>3.34</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S22" s="2" t="n">
-        <v>-4.34</v>
-      </c>
+        <v>3.78</v>
+      </c>
+      <c r="S22" s="2" t="n"/>
       <c r="T22" s="2" t="n">
-        <v>259.4</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>266</v>
-      </c>
+        <v>138.2</v>
+      </c>
+      <c r="U22" s="2" t="n"/>
       <c r="V22" s="2" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -2785,206 +2785,210 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>COMSYN</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Commercial Syn Bags Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>MENONBE</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Menon Bearings Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
-        <v>1162</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>289.17</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>289.77</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>86.28</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>109.39</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S23" s="2" t="n"/>
-      <c r="T23" s="2" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="U23" s="2" t="n"/>
-      <c r="V23" s="2" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="W23" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X23" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="n">
+        <v>1595</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>284.62</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>284.62</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>145.37</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>133.26</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>INDOBORAX</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Indo Borax &amp; Chemicals Limited</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>TMB</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Tamilnad Mercantile Bank Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1571</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>502.35</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>511.85</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>47.23</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>101.51</v>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="Q24" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R24" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S24" s="2" t="n"/>
-      <c r="T24" s="2" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="U24" s="2" t="n"/>
-      <c r="V24" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="W24" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="X24" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>14031</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>886.05</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>897.6</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>1446</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>1339</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
+      <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3013,51 +3017,51 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1931</v>
+        <v>2475</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>28.6</v>
+        <v>36.6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>271.32</v>
+        <v>294.95</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>271.32</v>
+        <v>294.95</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>53.49</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>68.5</v>
+        <v>93</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>79.26000000000001</v>
+        <v>101.19</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="n">
-        <v>77.3</v>
+        <v>97.8</v>
       </c>
       <c r="U25" s="2" t="n"/>
       <c r="V25" s="2" t="n">
@@ -3096,12 +3100,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TIMEX</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Timex Group India Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3115,63 +3119,65 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6057</v>
+        <v>10067</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>67.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>595.25</v>
+        <v>4580.3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>600</v>
+        <v>4580.3</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>60.17</v>
-      </c>
-      <c r="O26" s="2" t="n"/>
+        <v>52.28</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>82.34999999999999</v>
+      </c>
       <c r="P26" s="2" t="n">
-        <v>72.76000000000001</v>
+        <v>84.98</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>3.07</v>
+        <v>25.96</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>3.57</v>
+        <v>26.72</v>
       </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n">
-        <v>69.7</v>
+        <v>59</v>
       </c>
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="2" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>13.3</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3181,7 +3187,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3191,814 +3197,810 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>KENNAMET</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Kennametal India Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Rossell Techsys Limited</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>9051</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>4232</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>4232</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>66.18000000000001</v>
-      </c>
-      <c r="P27" s="2" t="n">
-        <v>70.91</v>
-      </c>
-      <c r="Q27" s="2" t="n">
-        <v>25.87</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="S27" s="2" t="n"/>
-      <c r="T27" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="W27" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="X27" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="n">
+        <v>4164</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>1104.6</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1108.9</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z27" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>Sep 2022</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>CANHLIFE</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Canara HSBC Life Insurance Company Limited</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>VOEPL</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Virtuoso Optoelectronics Limited</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Financial Services</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>14540</v>
-      </c>
-      <c r="G28" s="2" t="n">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1955</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>154.7</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>155.24</v>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n">
-        <v>9.390000000000001</v>
-      </c>
-      <c r="O28" s="2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P28" s="2" t="n">
-        <v>38.85</v>
-      </c>
-      <c r="Q28" s="2" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="R28" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="S28" s="2" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="U28" s="2" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="V28" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="W28" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="X28" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>570.65</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>579.55</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>ZELIO</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Zelio E Mobility Limited</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1905</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>882.95</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>882.95</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="n">
-        <v>83.91</v>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>238.49</v>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>443.02</v>
-      </c>
-      <c r="Q29" s="2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R29" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="S29" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="T29" s="2" t="n">
-        <v>441.3</v>
-      </c>
-      <c r="U29" s="2" t="n">
-        <v>447.4</v>
-      </c>
-      <c r="V29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="W29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>MODISONLTD</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>MODISON LIMITED</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>1340</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>412.8</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>414.85</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>194.79</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>157.49</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>CORONA</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>CORONA Remedies Limited</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IOL Chemicals and Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>12914</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>2149</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>2165.8</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>32.39</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="S30" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T30" s="2" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="U30" s="2" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="V30" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="W30" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="X30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5722</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>112.27</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z30" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>ONEGLOBAL</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>One Global Service Provider Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n">
-        <v>1080</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>553.95</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>564.1</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S31" s="2" t="n"/>
-      <c r="T31" s="2" t="n">
+      <c r="F31" s="3" t="n">
+        <v>10537</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U31" s="2" t="n"/>
-      <c r="V31" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="W31" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="X31" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="J31" s="3" t="n">
+        <v>1609.7</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>1609.7</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>77.42</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="U31" s="3" t="n"/>
+      <c r="V31" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>BLIL</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Balmer Lawrie Investments Limited</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>GHCL Textiles Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>1598</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>130.79</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>130.79</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>72.01000000000001</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>72.01000000000001</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="n">
-        <v>282</v>
-      </c>
-      <c r="W32" s="2" t="n">
-        <v>278</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="N32" s="3" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>DRAGARWQ</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>THELEELA</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n">
-        <v>2574</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>5373.5</v>
-      </c>
-      <c r="K33" s="2" t="n">
-        <v>5395</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="n">
+        <v>18543</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>561.7</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R33" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="W33" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="X33" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="N33" s="3" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="3" t="n">
+        <v>444</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>404</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SUNRAKSHAK</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Sunrakshakk Industries India Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>FREDUN</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Fredun Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
-        <v>1163</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>380.45</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>380.45</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="Q34" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="R34" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="n">
+      <c r="F34" s="3" t="n">
+        <v>2442</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>1476.6</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>1494.3</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U34" s="3" t="n"/>
+      <c r="V34" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="W34" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="X34" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="W34" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z34" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4008,17 +4010,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ASHIKAG</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ashika Global Securities Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4027,57 +4029,61 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>3175</v>
+        <v>7265</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>42.3</v>
+        <v>85</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>436.3</v>
+        <v>364.2</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>436.3</v>
+        <v>364.2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>147.29</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>182.63</v>
+      </c>
       <c r="P35" s="2" t="n">
-        <v>0.89</v>
+        <v>103.45</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>0.17</v>
+        <v>3.34</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>0.18</v>
+        <v>3.78</v>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n">
-        <v>0.7</v>
+        <v>100.1</v>
       </c>
       <c r="U35" s="2" t="n"/>
       <c r="V35" s="2" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>21.7</v>
+        <v>6</v>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
@@ -4101,210 +4107,210 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>VIJAYA</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Vijaya Diagnostic Centre Limited</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>ENTERO</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Entero Healthcare Solutions Limited</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>14995</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1482.4</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>1510.6</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S36" s="2" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="T36" s="2" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="U36" s="2" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="V36" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="W36" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="X36" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>7872</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1808.6</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>1808.6</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>47.92</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S36" s="3" t="n"/>
+      <c r="T36" s="3" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z36" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SJS</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>S.J.S. Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>YATHARTH</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>8152</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>2561.7</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>2561.7</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>37.78</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>90.28</v>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S37" s="2" t="n"/>
-      <c r="T37" s="2" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="W37" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="X37" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>9321</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>967.4</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>973.05</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="Z37" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4314,84 +4320,78 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>AFCOM</t>
+          <t>NIRLON</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Afcom Holdings Limited</t>
+          <t>Nirlon Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>4608</v>
+        <v>5792</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>31.4</v>
+        <v>16.2</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1608.8</v>
+        <v>642.65</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1608.8</v>
+        <v>647.95</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>70.20999999999999</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>86.69</v>
-      </c>
+        <v>2.53</v>
+      </c>
+      <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n">
-        <v>83.56999999999999</v>
+        <v>17.84</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S38" s="2" t="n">
-        <v>-4.34</v>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="U38" s="2" t="n">
-        <v>87.90000000000001</v>
-      </c>
+        <v>14.7</v>
+      </c>
+      <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="n">
-        <v>146</v>
+        <v>357</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>128</v>
+        <v>346</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>14.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MANINDS</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Man Industries (India) Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4439,61 +4439,61 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>5461</v>
+        <v>5826</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>26.7</v>
+        <v>47.6</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>718.1</v>
+        <v>50.03</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>728.5</v>
+        <v>50.58</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-1.43</v>
+        <v>-1.09</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>33.07</v>
+        <v>25.75</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>70.45</v>
+        <v>104.08</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>82.05</v>
+        <v>107.21</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>2.41</v>
+        <v>3.78</v>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="U39" s="2" t="n"/>
       <c r="V39" s="2" t="n">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>8.5</v>
+        <v>18.4</v>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
@@ -4522,84 +4522,84 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>AIRFLOA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pricol Limited</t>
+          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nifty Auto</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>9580</v>
+        <v>1121</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>35.8</v>
+        <v>28.6</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>790.9</v>
+        <v>467.65</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>806.55</v>
+        <v>467.65</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-1.94</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>39.86</v>
+        <v>52.25</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>27.02</v>
+        <v>79.62</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>77.41</v>
+        <v>67.44</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>1.99</v>
+        <v>0.04</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>2.41</v>
+        <v>0.44</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>14.47</v>
+        <v>-5.43</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>62.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>268</v>
+        <v>39</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>251</v>
+        <v>39</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR</t>
+          <t>VISHNU</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Limited</t>
+          <t>Vishnu Chemicals Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4647,57 +4647,61 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1948</v>
+        <v>4390</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>57.3</v>
+        <v>29.3</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>44.07</v>
+        <v>652.2</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>44.33</v>
+        <v>652.2</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-0.59</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>27.05</v>
+      </c>
       <c r="P41" s="2" t="n">
-        <v>6.4</v>
+        <v>30.25</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>-0.35</v>
+        <v>3.34</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>-0.29</v>
+        <v>3.78</v>
       </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n">
-        <v>6.8</v>
+        <v>26.9</v>
       </c>
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>17.9</v>
+        <v>5.6</v>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
@@ -4726,94 +4730,98 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Limited</t>
+          <t>PRIZOR</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>7503</v>
+        <v>1174</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>120</v>
+        <v>56.6</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1662.4</v>
+        <v>1087.4</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1689.8</v>
+        <v>1087.4</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="N42" s="2" t="n">
-        <v>72.43000000000001</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>127.92</v>
+        <v>215.51</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>179.21</v>
+        <v>293.99</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>1.99</v>
+        <v>4.38</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S42" s="2" t="n"/>
+        <v>4.82</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>-2.19</v>
+      </c>
       <c r="T42" s="2" t="n">
-        <v>177.2</v>
-      </c>
-      <c r="U42" s="2" t="n"/>
+        <v>289.6</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>296.2</v>
+      </c>
       <c r="V42" s="2" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -4828,12 +4836,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>Timex Group India Limited</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4847,65 +4855,63 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>5347</v>
+        <v>6600</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>82.2</v>
+        <v>74</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>382.9</v>
+        <v>653.75</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>382.9</v>
+        <v>653.75</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="N43" s="2" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="O43" s="2" t="n">
-        <v>102.25</v>
-      </c>
+        <v>47.34</v>
+      </c>
+      <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n">
-        <v>122.72</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>2.41</v>
+        <v>3.65</v>
       </c>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="2" t="n">
-        <v>120.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="U43" s="2" t="n"/>
       <c r="V43" s="2" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -4925,108 +4931,108 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>FRESHARA</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>FRESHARA</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>SME-NSE</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F44" s="2" t="n">
-        <v>2389</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1058.9</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>1058.9</v>
-      </c>
-      <c r="L44" s="2" t="n">
+      <c r="F44" s="3" t="n">
+        <v>1031</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>87.81</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>165.99</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>163.7</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>170.3</v>
-      </c>
-      <c r="V44" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="W44" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>127.41</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>124.16</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5042,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Ram Ratna Wires Limited</t>
+          <t>Canara HSBC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5051,69 +5057,73 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>4529</v>
+        <v>14648</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>485.85</v>
+        <v>154.19</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>487</v>
+        <v>156.89</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-0.24</v>
+        <v>-1.72</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="N45" s="2" t="n">
-        <v>3.48</v>
+        <v>12.55</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>52.28</v>
+        <v>6.9</v>
       </c>
       <c r="P45" s="2" t="n">
-        <v>42.53</v>
+        <v>38.39</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>1.99</v>
+        <v>-0.29</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S45" s="2" t="n"/>
+        <v>0.24</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>-4.55</v>
+      </c>
       <c r="T45" s="2" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U45" s="2" t="n"/>
+        <v>38.7</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>42.9</v>
+      </c>
       <c r="V45" s="2" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>17.4</v>
+        <v>3.9</v>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5133,104 +5143,100 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>KRISHANA</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Krishana Phoschem Limited</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>TAALTECH</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Taal Tech Limited</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>6113</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>199.68</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>199.68</v>
-      </c>
-      <c r="L46" s="2" t="n">
+      <c r="F46" s="3" t="n">
+        <v>1422</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>4562</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>4562</v>
+      </c>
+      <c r="L46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="O46" s="2" t="n">
-        <v>98.11</v>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="Q46" s="2" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R46" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="W46" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="X46" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
+      <c r="T46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -5240,12 +5246,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>BLIL</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>Balmer Lawrie Investments Limited</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5255,69 +5261,61 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>16546</v>
+        <v>1601</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>58.2</v>
+        <v>8.94</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>855.8</v>
+        <v>72.14</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>855.8</v>
+        <v>72.19</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n">
-        <v>67.81999999999999</v>
-      </c>
-      <c r="O47" s="2" t="n">
-        <v>164.31</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n">
-        <v>101.59</v>
+        <v>1.18</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>1.99</v>
+        <v>0.24</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S47" s="2" t="n">
-        <v>11.27</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="S47" s="2" t="n"/>
       <c r="T47" s="2" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="U47" s="2" t="n">
-        <v>90.3</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="U47" s="2" t="n"/>
       <c r="V47" s="2" t="n">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="W47" s="2" t="n">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>22.1</v>
+        <v>1.4</v>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
@@ -5346,17 +5344,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>RSL</t>
+          <t>ASHIKAG</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Rajputana Stainless Limited</t>
+          <t>Ashika Global Securities Limited</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5365,63 +5363,61 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1396</v>
+        <v>3227</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23.7</v>
+        <v>43</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>166.99</v>
+        <v>436.55</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>166.99</v>
+        <v>439.2</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n">
-        <v>26.53</v>
-      </c>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="n">
-        <v>47.74</v>
+        <v>0.95</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>10.77</v>
+        <v>0.24</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>11.62</v>
+        <v>0.26</v>
       </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="2" t="n">
-        <v>37</v>
+        <v>0.7</v>
       </c>
       <c r="U48" s="2" t="n"/>
       <c r="V48" s="2" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="W48" s="2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>16</v>
+        <v>21.7</v>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -5446,108 +5442,726 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
+          <t>AFCOM</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Afcom Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>4583</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1596.05</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1623.6</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="U50" s="2" t="n"/>
+      <c r="V50" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>MONOLITH</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2665</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1226</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1226</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>121.06</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>193.34</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>RAMRAT</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Ram Ratna Wires Limited</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>5525</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>591.9</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>591.9</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U52" s="2" t="n"/>
+      <c r="V52" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SHILPAMED</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Shilpa Medicare Limited</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>17677</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>903.8</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>903.8</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>165.45</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>121.32</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="W53" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Rajputana Stainless Limited</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>1483</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>177.49</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>177.49</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U54" s="2" t="n"/>
+      <c r="V54" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>AAYUSHBULL</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>1943</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>246</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="F55" s="2" t="n">
+        <v>1966</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>1266.9</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>1270.2</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>13.74</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>-4.34</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="V49" s="2" t="n">
+      <c r="I55" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>1283.65</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1283.65</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>-2.19</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="V55" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="W49" s="2" t="n">
+      <c r="W55" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="X49" s="2" t="n">
+      <c r="X55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z49" s="2" t="inlineStr">
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
+      <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB49"/>
+  <autoFilter ref="A1:AB55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5581,7 +6195,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-25 (prices as of 2026-08-24)</t>
+          <t>2026-08-28 (prices as of 2026-08-28)</t>
         </is>
       </c>
     </row>
@@ -5593,7 +6207,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2529 NSE mainboard (EQ) + 1025 NSE Emerge SME</t>
+          <t>2531 NSE mainboard (EQ) + 1035 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -5629,7 +6243,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3554 screened -&gt; 251 at ATH -&gt; 229 outperforming -&gt; 111 record PAT -&gt; 48 in mcap band</t>
+          <t>3566 screened -&gt; 250 at ATH -&gt; 236 outperforming -&gt; 111 record PAT -&gt; 54 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -84,8 +84,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -636,12 +636,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>OBSCP</t>
+          <t>DPEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -655,84 +655,84 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2238</v>
+        <v>1445</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>71.2</v>
+        <v>54.1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>866.05</v>
+        <v>578.75</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>873.3</v>
+        <v>590.05</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.83</v>
+        <v>-1.92</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>88.33</v>
+        <v>17.35</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>183.21</v>
+        <v>99.5</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>181.14</v>
+        <v>300.24</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4.82</v>
+        <v>2.35</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>-2.19</v>
+        <v>-2.73</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>176.8</v>
+        <v>298.3</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>183.3</v>
+        <v>303</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>31.5</v>
+        <v>27</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>27</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -742,103 +742,99 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1453</v>
+        <v>5997</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>33.1</v>
+        <v>49</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>605.85</v>
+        <v>51.51</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>605.85</v>
+        <v>51.51</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>37.09</v>
+        <v>26.47</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>72.83</v>
+        <v>135.1</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>111.8</v>
+        <v>116.8</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S3" s="3" t="n">
-        <v>-2.19</v>
-      </c>
+        <v>2.35</v>
+      </c>
+      <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>114</v>
-      </c>
+        <v>114.9</v>
+      </c>
+      <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -848,84 +844,80 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>YASHHV</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Yash Highvoltage Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2947</v>
+        <v>2549</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>75.7</v>
+        <v>37.7</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>986.1</v>
+        <v>304.75</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1003.7</v>
+        <v>306.02</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>-1.75</v>
+        <v>-0.42</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>36.38</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>115.09</v>
+        <v>117.23</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>106.41</v>
+        <v>112.24</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>-2.19</v>
-      </c>
+        <v>2.35</v>
+      </c>
+      <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>108.6</v>
-      </c>
+        <v>110.3</v>
+      </c>
+      <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
@@ -934,17 +926,17 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,203 +946,197 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CFF</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CFF FLUID CONTROL LIMITED</t>
+          <t>Cyient DLM Limited</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2175</v>
+        <v>6804</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>55.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1037.05</v>
+        <v>856.95</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1046.1</v>
+        <v>869.8</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.87</v>
+        <v>-1.48</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N5" s="2" t="n">
-        <v>44.02</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>95.08</v>
+        <v>189.8</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>63.1</v>
+        <v>99.22</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>-2.19</v>
-      </c>
+        <v>2.35</v>
+      </c>
+      <c r="S5" s="2" t="n"/>
       <c r="T5" s="2" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>65.3</v>
-      </c>
+        <v>97.3</v>
+      </c>
+      <c r="U5" s="2" t="n"/>
       <c r="V5" s="2" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="X5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>MACPOWER</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Macpower CNC Machines Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TIMEX</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Timex Group India Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="F6" s="3" t="n">
+        <v>6758</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>2007.1</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>2007.1</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>77.02</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>86.31999999999999</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>145.79</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="n">
+        <v>669.85</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>679.45</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n">
+        <v>94.41</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1162,12 +1148,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>KENNAMET</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Creative Newtech Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1181,61 +1167,61 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1865</v>
+        <v>10300</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>25.3</v>
+        <v>88</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1242.15</v>
+        <v>4688.5</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1264.15</v>
+        <v>4688.5</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>91.94</v>
+        <v>63.84</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>87.26000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>96.98</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>3.34</v>
+        <v>24.49</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>3.78</v>
+        <v>25.31</v>
       </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
@@ -1249,112 +1235,112 @@
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Sep 2022</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>MANINDS</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Limited</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>5762</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
+      <c r="F8" s="3" t="n">
+        <v>10336</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>768.2</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>768.2</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>96.59</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="W8" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="n">
+        <v>1578.7</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1609.7</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>82.38</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1366,12 +1352,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Azad Engineering Limited</t>
+          <t>Quality Power Electrical Equipments Limited</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1385,61 +1371,61 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18409</v>
+        <v>11582</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>132</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2850.5</v>
+        <v>1495.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2899.9</v>
+        <v>1495.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>36.23</v>
+        <v>39.49</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>61.87</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>85.73999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
@@ -1458,7 +1444,7 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1454,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Quality Power Electrical Equipments Limited</t>
+          <t>MMP Industries Limited</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1487,61 +1473,61 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>11084</v>
+        <v>1027</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>83.2</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1431.2</v>
+        <v>404.15</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1431.2</v>
+        <v>412.35</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>24.89</v>
+        <v>53.2</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>51.09</v>
+        <v>73.55</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>83.81999999999999</v>
+        <v>45.59</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>80.5</v>
+        <v>43.7</v>
       </c>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>186</v>
+        <v>39</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>5.4</v>
+        <v>28.2</v>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
@@ -1560,107 +1546,105 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>SEAMECLTD</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Seamec Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ELANTAS</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Elantas Beck India Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>4263</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
+      <c r="F11" s="2" t="n">
+        <v>9647</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>1676.6</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>1699</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>22.36</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>81.23999999999999</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="n">
+        <v>12219</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>12376.5</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1672,12 +1656,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>VADILALIND</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Vadilal Industries Limited</t>
+          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1687,65 +1671,69 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>5680</v>
+        <v>9545</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>25.9</v>
+        <v>52.7</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>7900</v>
+        <v>991.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>7900</v>
+        <v>1001.9</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>66.66</v>
+        <v>22.52</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>51.51</v>
+        <v>53.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>60.16</v>
+        <v>28.92</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>13.23</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U12" s="3" t="n"/>
+        <v>27</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V12" s="3" t="n">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>40.4</v>
+        <v>1.8</v>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
@@ -1764,111 +1752,107 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>SUDEEPPHRM</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Sudeep Pharma Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KSHINTL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>KSH International Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Chemicals</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>13013</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1152.1</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>1156.4</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>68.09</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>72.55</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7364</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1087.8</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1087.8</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>193.13</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>206.42</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n">
+        <v>209.1</v>
+      </c>
+      <c r="U13" s="2" t="n"/>
+      <c r="V13" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="inlineStr">
+      <c r="AA13" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB13" s="3" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1880,17 +1864,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>MENONBE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MMP Industries Limited</t>
+          <t>Menon Bearings Limited</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1899,61 +1883,61 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1027</v>
+        <v>1795</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>23</v>
+        <v>40.9</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>404.4</v>
+        <v>321.4</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>412.35</v>
+        <v>321.4</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-1.93</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>44.47</v>
+        <v>131.71</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>66.2</v>
+        <v>173.56</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>47.51</v>
+        <v>158.55</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>44.2</v>
+        <v>156.7</v>
       </c>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.2</v>
+        <v>15.8</v>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
@@ -1972,107 +1956,107 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>VINCOFE</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Vintage Coffee And Beverages Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>KAPSTON</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>2593</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>177.97</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>177.97</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>1777</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>584.05</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>73.28</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>109.86</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>141.59</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA15" s="3" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB15" s="3" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2084,12 +2068,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TURTLEMINT</t>
+          <t>SHADOWFAX</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Turtlemint Fintech Solutions Limited</t>
+          <t>Shadowfax Technologies Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2103,54 +2087,62 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4495</v>
-      </c>
-      <c r="G16" s="2" t="n"/>
+        <v>15232</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>90.09999999999999</v>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>152.65</v>
+        <v>259.55</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>153.64</v>
+        <v>264.84</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>116.38</v>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>12.77</v>
+        <v>136</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>2.3</v>
+        <v>0.75</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>2.47</v>
+        <v>1.66</v>
       </c>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n">
-        <v>10.5</v>
+        <v>135.2</v>
       </c>
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n">
-        <v>-144</v>
+        <v>169</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>-145</v>
-      </c>
-      <c r="X16" s="2" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>50.9</v>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
@@ -2168,7 +2160,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2178,80 +2170,84 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Bliss GVS Pharma Limited</t>
+          <t>Shilpa Medicare Limited</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Healthcare Index</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6250</v>
+        <v>18863</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45.4</v>
+        <v>66.3</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>588.1</v>
+        <v>964.15</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>588.1</v>
+        <v>964.15</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>41.14</v>
+        <v>79.19</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>157.67</v>
+        <v>189.45</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>261.24</v>
+        <v>129.03</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S17" s="3" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>13.23</v>
+      </c>
       <c r="T17" s="3" t="n">
-        <v>257.9</v>
-      </c>
-      <c r="U17" s="3" t="n"/>
+        <v>127.1</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>115.8</v>
+      </c>
       <c r="V17" s="3" t="n">
-        <v>142</v>
+        <v>298</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>135</v>
+        <v>244</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>5.2</v>
+        <v>22.1</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
@@ -2270,7 +2266,7 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2280,12 +2276,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
+          <t>SBC Exports Limited</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2299,61 +2295,61 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7741</v>
+        <v>2176</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>59.7</v>
+        <v>56.9</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3051.9</v>
+        <v>45.76</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3051.9</v>
+        <v>45.76</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>44.82</v>
+        <v>23.34</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>82.11</v>
+        <v>41.37</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>214.97</v>
+        <v>126.76</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n">
-        <v>211.6</v>
+        <v>124.9</v>
       </c>
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n">
-        <v>132</v>
+        <v>38.2</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>80</v>
+        <v>31.3</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
@@ -2372,209 +2368,213 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>AEROFLEX</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Aeroflex Industries Limited</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>SETL</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Standard Engineering Technology Limited</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
-        <v>7174</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
+      <c r="F19" s="3" t="n">
+        <v>8124</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="2" t="n">
-        <v>542.1</v>
-      </c>
-      <c r="K19" s="2" t="n">
-        <v>542.1</v>
-      </c>
-      <c r="L19" s="2" t="n">
+      <c r="J19" s="3" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>408.95</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="O19" s="2" t="n">
-        <v>127.67</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>207.89</v>
-      </c>
-      <c r="Q19" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R19" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S19" s="2" t="n"/>
-      <c r="T19" s="2" t="n">
-        <v>204.5</v>
-      </c>
-      <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="W19" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="X19" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>164.32</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>236.34</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>120.74</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="inlineStr">
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
+      <c r="AB19" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>RPEL</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Raghav Productivity Enhancers Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>TMB</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Tamilnad Mercantile Bank Limited</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>8029</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>14744</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="2" t="n">
-        <v>1748.4</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1748.4</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>80.66</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>143.72</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>204.52</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="n">
-        <v>201.2</v>
-      </c>
-      <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="W20" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="X20" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z20" s="2" t="inlineStr">
+      <c r="J20" s="3" t="n">
+        <v>932.45</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>942.45</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>119.14</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>1446</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>1339</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Avalon Technologies Limited</t>
+          <t>IOL Chemicals and Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2605,61 +2605,61 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>14910</v>
+        <v>5882</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>112</v>
+        <v>33.3</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2231.7</v>
+        <v>199.95</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2256.6</v>
+        <v>199.95</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>50.73</v>
+        <v>51.85</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>120.26</v>
+        <v>170.28</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>164.51</v>
+        <v>103.64</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>161.2</v>
+        <v>101.7</v>
       </c>
       <c r="U21" s="3" t="n"/>
       <c r="V21" s="3" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2688,81 +2688,85 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MARINE</t>
+          <t>SHREEREF</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marine Electricals (India) Limited</t>
+          <t>SHREE REFRIGERATIONS LIMITED</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5693</v>
+        <v>1503</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>406.8</v>
+        <v>419.9</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>406.8</v>
+        <v>421.35</v>
       </c>
       <c r="L22" s="2" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>133.28</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>100.48</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>95.63</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>141.51</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S22" s="2" t="n"/>
-      <c r="T22" s="2" t="n">
-        <v>138.2</v>
-      </c>
-      <c r="U22" s="2" t="n"/>
-      <c r="V22" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="W22" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="X22" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
@@ -2770,117 +2774,121 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>MENONBE</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Menon Bearings Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1595</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>The Karnataka Bank Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>12856</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>284.62</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>284.62</v>
-      </c>
-      <c r="L23" s="3" t="n">
+      <c r="J23" s="2" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="L23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>145.37</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>133.26</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n">
-        <v>129.9</v>
-      </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>1341</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z23" s="3" t="inlineStr">
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2892,12 +2900,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Tamilnad Mercantile Bank Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2907,73 +2915,69 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Nifty Financial Services</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>14031</v>
+        <v>5919</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>29</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>886.05</v>
+        <v>788.55</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>897.6</v>
+        <v>793.4</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-1.29</v>
+        <v>-0.61</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>31.63</v>
+        <v>46.69</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>29.58</v>
+        <v>94.25</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>108.7</v>
+        <v>90.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>1.29</v>
-      </c>
+        <v>2.35</v>
+      </c>
+      <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n">
-        <v>105.4</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>107.4</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="U24" s="3" t="n"/>
       <c r="V24" s="3" t="n">
-        <v>1446</v>
+        <v>204</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>1339</v>
+        <v>188</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2998,12 +3002,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Manorama Industries Limited</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3013,65 +3017,69 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty FMCG</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2475</v>
+        <v>12589</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>36.6</v>
+        <v>48.7</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>294.95</v>
+        <v>1993.4</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>294.95</v>
+        <v>1993.4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N25" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>35.05</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>93</v>
+        <v>47.43</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>101.19</v>
+        <v>50.46</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S25" s="2" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>-19.63</v>
+      </c>
       <c r="T25" s="2" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="U25" s="2" t="n"/>
+        <v>48.6</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>70.09999999999999</v>
+      </c>
       <c r="V25" s="2" t="n">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>64</v>
+        <v>226</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>4.7</v>
+        <v>14.2</v>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3098,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3108,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KENNAMET</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Kennametal India Limited</t>
+          <t>Deep Industries Limited</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3119,61 +3127,61 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>10067</v>
+        <v>5030</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>86</v>
+        <v>12.1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4580.3</v>
+        <v>786.45</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4580.3</v>
+        <v>786.45</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N26" s="2" t="n">
-        <v>52.28</v>
+        <v>47.75</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>82.34999999999999</v>
+        <v>132.88</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>84.98</v>
+        <v>43.23</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>25.96</v>
+        <v>1.9</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>26.72</v>
+        <v>2.35</v>
       </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="2" t="n">
-        <v>59</v>
+        <v>41.3</v>
       </c>
       <c r="U26" s="2" t="n"/>
       <c r="V26" s="2" t="n">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>3.5</v>
+        <v>13.7</v>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
@@ -3187,12 +3195,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3210,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ROSSTECH</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Rossell Techsys Limited</t>
+          <t>Canara HSBC Life Insurance Company Limited</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3217,69 +3225,73 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4164</v>
+        <v>14943</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1104.6</v>
+        <v>157.23</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1108.9</v>
+        <v>157.23</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>4.23</v>
+        <v>14.34</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>52.29</v>
+        <v>7.76</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>69.61</v>
+        <v>41.11</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.34</v>
+        <v>-1.46</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S27" s="3" t="n"/>
+        <v>-0.87</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>-5.4</v>
+      </c>
       <c r="T27" s="3" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="U27" s="3" t="n"/>
+        <v>42.6</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>46.5</v>
+      </c>
       <c r="V27" s="3" t="n">
-        <v>25.7</v>
+        <v>132</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>16.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3294,205 +3306,213 @@
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>VOEPL</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Virtuoso Optoelectronics Limited</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Vijaya Diagnostic Centre Limited</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>1955</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>15375</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>570.65</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>579.55</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
+      <c r="J28" s="2" t="n">
+        <v>1493.2</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1518.4</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA28" s="3" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB28" s="3" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>MODISONLTD</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>MODISON LIMITED</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>USHAMART</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Usha Martin Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>1340</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>414.85</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>194.79</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>157.49</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>154.2</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="n">
+        <v>15667</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>514.15</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>520.25</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n">
+        <v>508</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>467</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA29" s="3" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB29" s="3" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3504,12 +3524,12 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>TAALTECH</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IOL Chemicals and Pharmaceuticals Limited</t>
+          <t>Taal Tech Limited</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -3523,61 +3543,57 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5722</v>
+        <v>1404</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>32.4</v>
+        <v>22.6</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>194.95</v>
+        <v>4502.2</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>194.95</v>
+        <v>4562</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0</v>
+        <v>-1.31</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>160.83</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
       <c r="P30" s="3" t="n">
-        <v>112.27</v>
+        <v>7.29</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>3.34</v>
+        <v>-0.93</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>3.78</v>
+        <v>-0.86</v>
       </c>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n">
-        <v>108.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="3" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
@@ -3596,7 +3612,7 @@
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,80 +3622,84 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>KRN Heat Exchanger and Refrigeration Limited</t>
+          <t>MONOLITH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10537</v>
+        <v>2751</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>109</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1609.7</v>
+        <v>1265.65</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1609.7</v>
+        <v>1286.1</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>36.69</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>53.98</v>
+        <v>199.92</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>77.42</v>
+        <v>177.8</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S31" s="3" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>-2.73</v>
+      </c>
       <c r="T31" s="3" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="U31" s="3" t="n"/>
+        <v>175.9</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>180.5</v>
+      </c>
       <c r="V31" s="3" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>27.6</v>
+        <v>26.1</v>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
@@ -3698,7 +3718,7 @@
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3708,80 +3728,84 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>AFCOM</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>GHCL Textiles Limited</t>
+          <t>Afcom Holdings Limited</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1250</v>
+        <v>4715</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>13</v>
+        <v>32.1</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>130.79</v>
+        <v>1630.65</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>130.79</v>
+        <v>1652.35</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0</v>
+        <v>-1.31</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>25.15</v>
+        <v>81.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>63.31</v>
+        <v>103.6</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>69.63</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S32" s="3" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>-2.73</v>
+      </c>
       <c r="T32" s="3" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>80</v>
+      </c>
       <c r="V32" s="3" t="n">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>35.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
@@ -3800,205 +3824,203 @@
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>THELEELA</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Leela Palaces Hotels &amp; Resorts Limited</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>18543</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
+      <c r="F33" s="2" t="n">
+        <v>2077</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>555.25</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>561.7</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>33.62</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>25.58</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>35.57</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" s="3" t="n">
-        <v>444</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>404</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
+      <c r="J33" s="2" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>138.96</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>167.03</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>75.79000000000001</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="X33" s="2" t="n"/>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA33" s="3" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
+      <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>FREDUN</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Fredun Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>2442</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
+      <c r="F34" s="2" t="n">
+        <v>1489</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>1476.6</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>1494.3</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
+      <c r="J34" s="2" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA34" s="3" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB34" s="3" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4010,12 +4032,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>ULTRAMAR</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Ultramarine &amp; Pigments Limited</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4029,61 +4051,59 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>7265</v>
+        <v>1277</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>85</v>
+        <v>14.2</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>364.2</v>
+        <v>437.15</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>364.2</v>
+        <v>442.85</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="N35" s="2" t="n">
-        <v>147.29</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>182.63</v>
-      </c>
+        <v>12.64</v>
+      </c>
+      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n">
-        <v>103.45</v>
+        <v>6.48</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>3.34</v>
+        <v>1.14</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>3.78</v>
+        <v>1.71</v>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="2" t="n">
-        <v>100.1</v>
+        <v>5.3</v>
       </c>
       <c r="U35" s="2" t="n"/>
       <c r="V35" s="2" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W35" s="2" t="n">
         <v>83</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>6</v>
+        <v>10.8</v>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
@@ -4102,213 +4122,209 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>ENTERO</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Entero Healthcare Solutions Limited</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SAKAR</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Sakar Healthcare Limited</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>7872</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
+      <c r="F36" s="2" t="n">
+        <v>2256</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>1808.6</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>1808.6</v>
-      </c>
-      <c r="L36" s="3" t="n">
+      <c r="J36" s="2" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="L36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>47.92</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>65.20999999999999</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S36" s="3" t="n"/>
-      <c r="T36" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="U36" s="3" t="n"/>
-      <c r="V36" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>92.04000000000001</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>197.37</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z36" s="3" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA36" s="3" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB36" s="3" t="inlineStr">
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>9321</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="n">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>3266</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>967.4</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>973.05</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>19.65</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="Q37" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y37" s="3" t="inlineStr">
+      <c r="J37" s="2" t="n">
+        <v>480.85</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>480.85</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>187.66</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>247.99</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>159.74</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="n">
+        <v>157.8</v>
+      </c>
+      <c r="U37" s="2" t="n"/>
+      <c r="V37" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z37" s="3" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA37" s="3" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB37" s="3" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4320,12 +4336,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>NIRLON</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nirlon Limited</t>
+          <t>Asian Energy Services Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4339,63 +4355,65 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5792</v>
+        <v>2516</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>16.2</v>
+        <v>39</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>4</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>642.65</v>
+        <v>517.45</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>647.95</v>
+        <v>523</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-0.82</v>
+        <v>-1.06</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="O38" s="2" t="n"/>
+        <v>35.42</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>81.23999999999999</v>
+      </c>
       <c r="P38" s="2" t="n">
-        <v>17.84</v>
+        <v>38.62</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>3.65</v>
+        <v>2.35</v>
       </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="2" t="n">
-        <v>14.7</v>
+        <v>36.7</v>
       </c>
       <c r="U38" s="2" t="n"/>
       <c r="V38" s="2" t="n">
-        <v>357</v>
+        <v>60</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>346</v>
+        <v>53</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4410,7 +4428,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4438,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FCL</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4439,65 +4457,61 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>5826</v>
+        <v>2622</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>47.6</v>
+        <v>34.4</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>50.03</v>
+        <v>5422.5</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>50.58</v>
+        <v>5422.5</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-1.09</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>104.08</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n">
-        <v>107.21</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>3.34</v>
+        <v>-0.93</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>3.78</v>
+        <v>-0.86</v>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="2" t="n">
-        <v>103.9</v>
+        <v>2.8</v>
       </c>
       <c r="U39" s="2" t="n"/>
       <c r="V39" s="2" t="n">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>18.4</v>
+        <v>7.1</v>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -4512,7 +4526,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4522,84 +4536,80 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>AIRFLOA</t>
+          <t>INDOBORAX</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
+          <t>Indo Borax &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1121</v>
+        <v>1652</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>28.6</v>
+        <v>33.8</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>467.65</v>
+        <v>514.9</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>467.65</v>
+        <v>516.05</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>52.25</v>
+        <v>40.15</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>79.62</v>
+        <v>109.39</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>67.44</v>
+        <v>112.55</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>0.04</v>
+        <v>1.9</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S40" s="2" t="n">
-        <v>-5.43</v>
-      </c>
+        <v>2.35</v>
+      </c>
+      <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="U40" s="2" t="n">
-        <v>72.90000000000001</v>
-      </c>
+        <v>110.6</v>
+      </c>
+      <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
@@ -4608,17 +4618,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4638,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VISHNU</t>
+          <t>COMSYN</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Vishnu Chemicals Limited</t>
+          <t>Commercial Syn Bags Limited</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4647,61 +4657,61 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>4390</v>
+        <v>1218</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>29.3</v>
+        <v>41</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>652.2</v>
+        <v>301.3</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>652.2</v>
+        <v>304.35</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="N41" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>96.92</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>27.05</v>
+        <v>96.86</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>30.25</v>
+        <v>97.08</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>3.34</v>
+        <v>1.9</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>3.78</v>
+        <v>2.35</v>
       </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="2" t="n">
-        <v>26.9</v>
+        <v>95.2</v>
       </c>
       <c r="U41" s="2" t="n"/>
       <c r="V41" s="2" t="n">
-        <v>150</v>
+        <v>29.7</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
@@ -4720,211 +4730,209 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>PRIZOR</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>PRIZOR</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>1174</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1087.4</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>1087.4</v>
-      </c>
-      <c r="L42" s="2" t="n">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>BLISSGVS</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Bliss GVS Pharma Limited</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>7158</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>671</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>671</v>
+      </c>
+      <c r="L42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>65.06999999999999</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>215.51</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>293.99</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S42" s="2" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="T42" s="2" t="n">
-        <v>289.6</v>
-      </c>
-      <c r="U42" s="2" t="n">
-        <v>296.2</v>
-      </c>
-      <c r="V42" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="W42" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="X42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>213.71</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>329.55</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S42" s="3" t="n"/>
+      <c r="T42" s="3" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="U42" s="3" t="n"/>
+      <c r="V42" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>TIMEX</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Timex Group India Limited</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>MARINE</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Marine Electricals (India) Limited</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>6600</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
+      <c r="F43" s="3" t="n">
+        <v>6048</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J43" s="2" t="n">
-        <v>653.75</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>653.75</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>47.34</v>
-      </c>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n">
-        <v>89.73999999999999</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="W43" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="X43" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="J43" s="3" t="n">
+        <v>432.15</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>432.6</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>73.66</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>125.37</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>146.89</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
+      <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB43" s="2" t="inlineStr">
+      <c r="AB43" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4936,12 +4944,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>ACCENTMIC</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -4955,62 +4963,62 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1031</v>
+        <v>1482</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>28.5</v>
+        <v>33.8</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>438.9</v>
+        <v>617.8</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>438.9</v>
+        <v>617.8</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>120.94</v>
+        <v>29.41</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>127.41</v>
+        <v>80.12</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>124.16</v>
+        <v>117.61</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>4.38</v>
+        <v>1.9</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>4.82</v>
+        <v>2.35</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>-2.19</v>
+        <v>-2.73</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.8</v>
+        <v>115.7</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>126.3</v>
+        <v>120.3</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>0</v>
@@ -5032,111 +5040,107 @@
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>CANHLIFE</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Canara HSBC Life Insurance Company Limited</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>SEAMECLTD</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Seamec Limited</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Financial Services</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>14648</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>154.19</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>156.89</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="Q45" s="2" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="R45" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="S45" s="2" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="T45" s="2" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="U45" s="2" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="V45" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="W45" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="X45" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y45" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>4561</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>1793.6</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1793.6</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>91.76000000000001</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S45" s="3" t="n"/>
+      <c r="T45" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="U45" s="3" t="n"/>
+      <c r="V45" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
+      <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
+      <c r="AB45" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -5148,12 +5152,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>TAALTECH</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Taal Tech Limited</t>
+          <t>Sudeep Pharma Limited</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -5163,61 +5167,69 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Nifty Chemicals</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>1422</v>
+        <v>14985</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>22.9</v>
+        <v>82</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>4562</v>
+        <v>1329.3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>4562</v>
+        <v>1329.3</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>127.91</v>
+      </c>
       <c r="P46" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0.24</v>
+        <v>-2.84</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+        <v>-2.17</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>4.52</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
+        <v>74.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>67.2</v>
+      </c>
       <c r="V46" s="3" t="n">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
@@ -5236,925 +5248,925 @@
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>BLIL</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Balmer Lawrie Investments Limited</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>ROSSTECH</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Rossell Techsys Limited</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>1601</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
+      <c r="F47" s="3" t="n">
+        <v>4341</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J47" s="2" t="n">
-        <v>72.14</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>72.19</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Q47" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="R47" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S47" s="2" t="n"/>
-      <c r="T47" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="U47" s="2" t="n"/>
-      <c r="V47" s="2" t="n">
-        <v>282</v>
-      </c>
-      <c r="W47" s="2" t="n">
-        <v>278</v>
-      </c>
-      <c r="X47" s="2" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="J47" s="3" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>1150.5</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="Q47" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S47" s="3" t="n"/>
+      <c r="T47" s="3" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="U47" s="3" t="n"/>
+      <c r="V47" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
+      <c r="Z47" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
+      <c r="AA47" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB47" s="2" t="inlineStr">
+      <c r="AB47" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>ASHIKAG</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Ashika Global Securities Limited</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>ENTERO</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Entero Healthcare Solutions Limited</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="2" t="n">
-        <v>3227</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>436.55</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>439.2</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q48" s="2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="R48" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="S48" s="2" t="n"/>
-      <c r="T48" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U48" s="2" t="n"/>
-      <c r="V48" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="n">
+        <v>7956</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>1827.6</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>1848</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="Q48" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S48" s="3" t="n"/>
+      <c r="T48" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U48" s="3" t="n"/>
+      <c r="V48" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Z48" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA48" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB48" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>AFCOM</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Afcom Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>AIRFLOA</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>4583</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
+      <c r="F49" s="3" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J49" s="2" t="n">
-        <v>1596.05</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>1623.6</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>71.67</v>
-      </c>
-      <c r="O49" s="2" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="Q49" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="R49" s="2" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S49" s="2" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="T49" s="2" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="U49" s="2" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="W49" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="X49" s="2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="Y49" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z49" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr">
+      <c r="J49" s="3" t="n">
+        <v>487.2</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>487.2</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="Q49" s="3" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>SHUKRAPHAR</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Shukra Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>VISHNU</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Vishnu Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>1947</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="L50" s="2" t="n">
+      <c r="F50" s="3" t="n">
+        <v>4719</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>702</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>702</v>
+      </c>
+      <c r="L50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q50" s="2" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="R50" s="2" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="S50" s="2" t="n"/>
-      <c r="T50" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="U50" s="2" t="n"/>
-      <c r="V50" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="W50" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X50" s="2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="Q50" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S50" s="3" t="n"/>
+      <c r="T50" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="U50" s="3" t="n"/>
+      <c r="V50" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z50" s="2" t="inlineStr">
+      <c r="Z50" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
+      <c r="AA50" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB50" s="2" t="inlineStr">
+      <c r="AB50" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>MONOLITH</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>PRIZOR</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>PRIZOR</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>SME-NSE</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F51" s="2" t="n">
-        <v>2665</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>1226</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>1226</v>
-      </c>
-      <c r="L51" s="2" t="n">
+      <c r="F51" s="3" t="n">
+        <v>1296</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>1200.4</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>1200.4</v>
+      </c>
+      <c r="L51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="n">
-        <v>121.06</v>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>193.34</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>191.9</v>
-      </c>
-      <c r="Q51" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="R51" s="2" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S51" s="2" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="T51" s="2" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="U51" s="2" t="n">
-        <v>194.1</v>
-      </c>
-      <c r="V51" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="W51" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="X51" s="2" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Y51" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z51" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>53.98</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>211.35</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>285.79</v>
+      </c>
+      <c r="Q51" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>RAMRAT</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Ram Ratna Wires Limited</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>BLIL</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Balmer Lawrie Investments Limited</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="2" t="n">
-        <v>5525</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J52" s="2" t="n">
-        <v>591.9</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>591.9</v>
-      </c>
-      <c r="L52" s="2" t="n">
+      <c r="F52" s="3" t="n">
+        <v>1611</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="L52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="n">
-        <v>22.53</v>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>79.54000000000001</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="Q52" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R52" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S52" s="2" t="n"/>
-      <c r="T52" s="2" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="U52" s="2" t="n"/>
-      <c r="V52" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="W52" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="X52" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y52" s="2" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="n"/>
+      <c r="O52" s="3" t="n"/>
+      <c r="P52" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q52" s="3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="S52" s="3" t="n"/>
+      <c r="T52" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U52" s="3" t="n"/>
+      <c r="V52" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="W52" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="X52" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="Z52" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
+      <c r="AA52" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
+      <c r="AB52" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SHILPAMED</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Shilpa Medicare Limited</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>17677</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J53" s="2" t="n">
-        <v>903.8</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>903.8</v>
-      </c>
-      <c r="L53" s="2" t="n">
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2280</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="L53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="n">
-        <v>83.38</v>
-      </c>
-      <c r="O53" s="2" t="n">
-        <v>165.45</v>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>121.32</v>
-      </c>
-      <c r="Q53" s="2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R53" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S53" s="2" t="n">
-        <v>15.78</v>
-      </c>
-      <c r="T53" s="2" t="n">
-        <v>118</v>
-      </c>
-      <c r="U53" s="2" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="V53" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="W53" s="2" t="n">
-        <v>244</v>
-      </c>
-      <c r="X53" s="2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="n"/>
+      <c r="O53" s="3" t="n"/>
+      <c r="P53" s="3" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="Q53" s="3" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="S53" s="3" t="n"/>
+      <c r="T53" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="U53" s="3" t="n"/>
+      <c r="V53" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z53" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA53" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
+      <c r="AB53" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Rajputana Stainless Limited</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
-        <v>1483</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="F54" s="3" t="n">
+        <v>1516</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>177.49</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>177.49</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="Q54" s="2" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="R54" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="S54" s="2" t="n"/>
-      <c r="T54" s="2" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="n">
+      <c r="I54" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>181.56</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="O54" s="3" t="n"/>
+      <c r="P54" s="3" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="Q54" s="3" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="S54" s="3" t="n"/>
+      <c r="T54" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="U54" s="3" t="n"/>
+      <c r="V54" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="W54" s="2" t="n">
+      <c r="W54" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="X54" s="2" t="n">
+      <c r="X54" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="Y54" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Z54" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA54" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
+      <c r="AB54" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>AAYUSHBULL</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
-        <v>1966</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="F55" s="3" t="n">
+        <v>1941</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J55" s="2" t="n">
+      <c r="I55" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>1267.7</v>
+      </c>
+      <c r="K55" s="3" t="n">
         <v>1283.65</v>
       </c>
-      <c r="K55" s="2" t="n">
-        <v>1283.65</v>
-      </c>
-      <c r="L55" s="2" t="n">
+      <c r="L55" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="Q55" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X55" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="O55" s="2" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="Q55" s="2" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="R55" s="2" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="S55" s="2" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="T55" s="2" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="U55" s="2" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="V55" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W55" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y55" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Z55" s="3" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
+      <c r="AA55" s="3" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
+      <c r="AB55" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6195,7 +6207,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-28 (prices as of 2026-08-28)</t>
+          <t>2026-09-04 (prices as of 2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6219,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2531 NSE mainboard (EQ) + 1035 NSE Emerge SME</t>
+          <t>2542 NSE mainboard (EQ) + 1048 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6255,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3566 screened -&gt; 250 at ATH -&gt; 236 outperforming -&gt; 111 record PAT -&gt; 54 in mcap band</t>
+          <t>3590 screened -&gt; 234 at ATH -&gt; 229 outperforming -&gt; 114 record PAT -&gt; 54 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB44"/>
+  <dimension ref="A1:AB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,17 +636,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>SAKAR</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bliss GVS Pharma Limited</t>
+          <t>Sakar Healthcare Limited</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -655,61 +655,61 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7630</v>
+        <v>2625</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>55.4</v>
+        <v>72.7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>720.95</v>
+        <v>1179.8</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>722.3</v>
+        <v>1179.8</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>64.66</v>
+        <v>46.81</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>254.55</v>
+        <v>122.18</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>369.8</v>
+        <v>245.07</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n">
-        <v>370.8</v>
+        <v>247.9</v>
       </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5.2</v>
+        <v>16.1</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -733,104 +733,104 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>SAKAR</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Sakar Healthcare Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>AVALON</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Avalon Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>2578</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="F3" s="3" t="n">
+        <v>16947</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>1158.55</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>1158.55</v>
-      </c>
-      <c r="L3" s="2" t="n">
+      <c r="J3" s="3" t="n">
+        <v>2537.7</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>2537.7</v>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>40.58</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>123.33</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>239.45</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n">
-        <v>240.5</v>
-      </c>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="W3" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="X3" s="2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>166.59</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n">
+        <v>159.5</v>
+      </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -859,56 +859,56 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>18791</v>
+        <v>19991</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>961.15</v>
+        <v>1021.1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>964.15</v>
+        <v>1021.1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>75.79000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>207.27</v>
+        <v>215.89</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>129.76</v>
+        <v>149.78</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>12.31</v>
+        <v>11.84</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>130.8</v>
+        <v>152.7</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>117.4</v>
+        <v>137.9</v>
       </c>
       <c r="V4" s="2" t="n">
         <v>298</v>
@@ -946,12 +946,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>RACLGEAR</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>RACL Geartech Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -965,65 +965,65 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2067</v>
+        <v>2105</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>41.5</v>
+        <v>54.1</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1756.7</v>
+        <v>2104.5</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1756.7</v>
+        <v>2104.5</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>37.52</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>42.83</v>
+        <v>147.65</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>93.19</v>
+        <v>142.54</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>94.2</v>
+        <v>145.4</v>
       </c>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n">
-        <v>49.6</v>
+        <v>38.9</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>1.2</v>
+        <v>14.4</v>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1043,206 +1043,206 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>AZAD</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Azad Engineering Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>KOVAI</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Kovai Medical Center &amp; Hospital Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>18402</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="F6" s="2" t="n">
+        <v>6779</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>2849.1</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>2899.9</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>32.51</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>90.87</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>76.23999999999999</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="n">
+        <v>6226</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>6292</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>141.63</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>141.63</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>MMP</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>MMP Industries Limited</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>MENONBE</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Menon Bearings Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>1194</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
+      <c r="F7" s="3" t="n">
+        <v>1772</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>469.95</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>478.5</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>123.47</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="n">
+        <v>316.85</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>80.61</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>168.27</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>139.31</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="Z7" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ELANTAS</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Elantas Beck India Limited</t>
+          <t>SBC Exports Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1271,63 +1271,65 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11504</v>
+        <v>2343</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>64.8</v>
+        <v>61.3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14513</v>
+        <v>49.24</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>14513</v>
+        <v>49.24</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="O8" s="2" t="n"/>
+        <v>12.96</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>55.77</v>
+      </c>
       <c r="P8" s="2" t="n">
-        <v>57.36</v>
+        <v>130.31</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-0.54</v>
+        <v>-2.88</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.13</v>
+        <v>-2.38</v>
       </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n">
-        <v>57.9</v>
+        <v>133.2</v>
       </c>
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n">
-        <v>177</v>
+        <v>38.2</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>151</v>
+        <v>31.3</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>17.2</v>
+        <v>22</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1352,80 +1354,84 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>AIRFLOA</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3888</v>
+        <v>1400</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>20.3</v>
+        <v>35.8</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>87.41</v>
+        <v>584.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>87.41</v>
+        <v>584.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>68.36</v>
+        <v>72.66</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>115.67</v>
+        <v>106.98</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>54.49</v>
+        <v>109.17</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
+        <v>-2.38</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-4.03</v>
+      </c>
       <c r="T9" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="U9" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>113.2</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
@@ -1434,12 +1440,12 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
@@ -1454,12 +1460,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SMSPHARMA</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>SMS Pharmaceuticals Limited</t>
+          <t>Timex Group India Limited</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1473,65 +1479,63 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>4323</v>
+        <v>7208</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>42.2</v>
+        <v>80.8</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>463.45</v>
+        <v>714.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>463.45</v>
+        <v>714.2</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>25.68</v>
-      </c>
+        <v>37.69</v>
+      </c>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n">
-        <v>54.19</v>
+        <v>107.28</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-1.02</v>
+        <v>0.13</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-0.47</v>
+        <v>0.74</v>
       </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>55.2</v>
+        <v>107.2</v>
       </c>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1551,108 +1555,104 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>BLUESTONE</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>BlueStone Jewellery and Lifestyle Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>COMSYN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Syn Bags Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Consumer Durables</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13606</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1239</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>890.35</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>894.5</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>71.06</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>39.41</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>308.3</v>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="J11" s="2" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="inlineStr">
+      <c r="AA11" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1662,98 +1662,98 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>FLYSBS</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>FLYSBS</t>
+          <t>Lumax Auto Technologies Limited</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Auto</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1216</v>
+        <v>14318</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>20</v>
+        <v>43.2</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>702.65</v>
+        <v>2102.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>705.2</v>
+        <v>2102.7</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.36</v>
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>68.8</v>
+        <v>27.72</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>75.81999999999999</v>
+        <v>34.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>13.88</v>
+        <v>89.53</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>-1.75</v>
+        <v>-0.73</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>14.9</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>15.6</v>
+        <v>90.3</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>61</v>
+        <v>383</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>61</v>
+        <v>338</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>EBGNG</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>KSH International Limited</t>
+          <t>GNG Electronics Limited</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1787,65 +1787,65 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>7937</v>
+        <v>8023</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>60.6</v>
+        <v>56.3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1170.9</v>
+        <v>703.05</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1176.75</v>
+        <v>703.05</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>42.8</v>
+        <v>40.06</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>202.25</v>
+        <v>84.84</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>229.83</v>
+        <v>79.92</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>-4.3</v>
+        <v>-2.88</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>-3.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n">
-        <v>234.1</v>
+        <v>82.8</v>
       </c>
       <c r="U13" s="2" t="n"/>
       <c r="V13" s="2" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>17.1</v>
+        <v>7.5</v>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>AEROFLEX</t>
+          <t>MWL</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Aeroflex Industries Limited</t>
+          <t>Mangalam Worldwide Limited</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1889,61 +1889,61 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>7471</v>
+        <v>1262</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>111</v>
+        <v>24.3</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>563.95</v>
+        <v>42.52</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>573.5</v>
+        <v>43.04</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.21</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>25.85</v>
+        <v>13.13</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>140.81</v>
+        <v>60.06</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>217.58</v>
+        <v>66.78</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n">
-        <v>218.6</v>
+        <v>69.7</v>
       </c>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>19.6</v>
+        <v>4</v>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>ELANTAS</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Elantas Beck India Limited</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1991,65 +1991,63 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1790</v>
+        <v>11235</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>58.7</v>
+        <v>63.3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>588.2</v>
+        <v>14228</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>588.4</v>
+        <v>14513</v>
       </c>
       <c r="L15" s="2" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="R15" s="2" t="n">
         <v>-0.03</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>73.41</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>117.57</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>144.22</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <v>-0.47</v>
       </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n">
-        <v>145.2</v>
+        <v>54.9</v>
       </c>
       <c r="U15" s="2" t="n"/>
       <c r="V15" s="2" t="n">
-        <v>30.5</v>
+        <v>177</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>28.1</v>
+        <v>151</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>8.5</v>
+        <v>17.2</v>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2069,312 +2067,320 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>AIMTRON</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>AIMTRON</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>3772</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>1772.95</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>1772.95</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CORONA</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CORONA Remedies Limited</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>13505</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>2201.8</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>2236.1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="N16" s="3" t="n">
-        <v>40.43</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>136.14</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>142.62</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>144.4</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="N16" s="2" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>MANINDS</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ALIVUS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Alivus Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>6485</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>866.1</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>876.45</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>58.64</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>118.88</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>112.98</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="W17" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="X17" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>17576</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1430.8</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1443.7</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>603</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>565</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>NEPHROPLUS</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Nephrocare Health Services Limited</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Vijaya Diagnostic Centre Limited</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>7695</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>765.35</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>765.35</v>
-      </c>
-      <c r="L18" s="3" t="n">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>16047</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1558.9</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1558.9</v>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>42.18</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>-1.81</v>
-      </c>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z18" s="3" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2390,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>AYE</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>VA Tech Wabag Limited</t>
+          <t>Aye Finance Limited</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2403,65 +2409,65 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>14244</v>
+        <v>4584</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>35.8</v>
+        <v>19.3</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2277.9</v>
+        <v>185.72</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2277.9</v>
+        <v>189.13</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>44.37</v>
+        <v>12.71</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>85.56</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>49.73</v>
+        <v>44.07</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.69</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>-0.47</v>
+        <v>-1.81</v>
       </c>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>50.8</v>
+        <v>46.8</v>
       </c>
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="3" t="n">
-        <v>394</v>
+        <v>238</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>370</v>
+        <v>195</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.5</v>
+        <v>22.1</v>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2486,84 +2492,80 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>VISHNU</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Sri Lotus Developers and Realty Limited</t>
+          <t>Vishnu Chemicals Limited</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Nifty Realty</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>10271</v>
+        <v>4864</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>209.27</v>
+        <v>722.15</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>209.77</v>
+        <v>731.55</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.24</v>
+        <v>-1.28</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>56.13</v>
+        <v>20.16</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>75.18000000000001</v>
+        <v>40.69</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>17.35</v>
+        <v>43.78</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>-3.99</v>
-      </c>
+        <v>-2.38</v>
+      </c>
+      <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>21.3</v>
-      </c>
+        <v>46.7</v>
+      </c>
+      <c r="U20" s="3" t="n"/>
       <c r="V20" s="3" t="n">
-        <v>263</v>
+        <v>150</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>243</v>
+        <v>142</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
@@ -2592,12 +2594,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SUNRAKSHAK</t>
+          <t>SHUKRAPHAR</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Sunrakshakk Industries India Limited</t>
+          <t>Shukra Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2611,57 +2613,57 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1171</v>
+        <v>2464</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>26.9</v>
+        <v>72.5</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>377.05</v>
+        <v>55.93</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>380.45</v>
+        <v>56.1</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.3</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="n">
-        <v>0.03</v>
+        <v>35.03</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-2.58</v>
+        <v>-3.2</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-2.4</v>
+        <v>-3.02</v>
       </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n">
-        <v>2.6</v>
+        <v>38.2</v>
       </c>
       <c r="U21" s="3" t="n"/>
       <c r="V21" s="3" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>22.9</v>
+        <v>17.9</v>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
@@ -2690,84 +2692,80 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>PCCL</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>PCCL</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1072</v>
+        <v>4348</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>42.3</v>
+        <v>26</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>434</v>
+        <v>147.57</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>440.55</v>
+        <v>147.57</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-1.49</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>55.56</v>
+        <v>34.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>93.70999999999999</v>
+        <v>56.19</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>129.81</v>
+        <v>19.4</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>-2.38</v>
+      </c>
+      <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n">
-        <v>130.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>131.6</v>
-      </c>
+        <v>22.3</v>
+      </c>
+      <c r="U22" s="3" t="n"/>
       <c r="V22" s="3" t="n">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
@@ -2776,12 +2774,12 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
@@ -2796,12 +2794,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>CORONA Remedies Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2811,73 +2809,65 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>13680</v>
+        <v>2565</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>64.5</v>
+        <v>33.6</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2236.1</v>
+        <v>5371.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2236.1</v>
+        <v>5422.5</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>29.38</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>45.33</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
       <c r="P23" s="3" t="n">
-        <v>55.46</v>
+        <v>0.95</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>-3.62</v>
+        <v>-2.69</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>-2.78</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>12.11</v>
-      </c>
+        <v>-2.55</v>
+      </c>
+      <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>43.4</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="U23" s="3" t="n"/>
       <c r="V23" s="3" t="n">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -2897,206 +2887,214 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>INDNIPPON</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>India Nippon Electricals Limited</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>3067</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>1358.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1369</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>52.64</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>78.22</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>44.63</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="X24" s="3" t="n">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>DPEL</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>DPEL</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1619</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>648.5</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>648.5</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>164.69</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB24" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Standard Engineering Technology Limited</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>9340</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>468.15</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>468.15</v>
-      </c>
-      <c r="L25" s="2" t="n">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SACHEEROME</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>SACHEEROME</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1201</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>536.85</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>536.85</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>194.62</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>303.2</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>149.51</v>
-      </c>
-      <c r="Q25" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R25" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S25" s="2" t="n"/>
-      <c r="T25" s="2" t="n">
-        <v>150.5</v>
-      </c>
-      <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="W25" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="X25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>65.69</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>134.64</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3106,17 +3104,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>YASHHV</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>FRESHARA</t>
+          <t>Yash Highvoltage Limited</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3125,69 +3123,69 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1140</v>
+        <v>3166</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>31.5</v>
+        <v>81.3</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>485</v>
+        <v>1059.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>486.4</v>
+        <v>1080.45</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.29</v>
+        <v>-1.97</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>119.06</v>
+        <v>26.81</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>171.4</v>
+        <v>126.32</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>146.38</v>
+        <v>117.94</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.75</v>
+        <v>-4.03</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>147.4</v>
+        <v>120.8</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>148.1</v>
+        <v>122</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
@@ -3212,12 +3210,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KOVAI</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Kovai Medical Center &amp; Hospital Limited</t>
+          <t>Quality Power Electrical Equipments Limited</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3231,65 +3229,65 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6775</v>
+        <v>11904</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>26.4</v>
+        <v>89.3</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6203.5</v>
+        <v>1536.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6292</v>
+        <v>1536.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>6.75</v>
+        <v>16.32</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>140.76</v>
+        <v>84.06</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>140.76</v>
+        <v>55.34</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>22.41</v>
+        <v>-2.88</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>23.35</v>
+        <v>-2.38</v>
       </c>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n">
-        <v>118.3</v>
+        <v>58.2</v>
       </c>
       <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="n">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -3309,104 +3307,100 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Spectrum Electrical Industries Limited</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TAALTECH</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Taal Tech Limited</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>4767</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>3022.5</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>3022.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
+      <c r="F28" s="2" t="n">
+        <v>1676</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>5416.3</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>5416.3</v>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>89.08</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>106.29</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>119.91</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z28" s="3" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA28" s="3" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB28" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3416,12 +3410,12 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>ALGOQUANT</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>GNG Electronics Limited</t>
+          <t>Algoquant Fintech Limited</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3435,61 +3429,61 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7767</v>
+        <v>2037</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.5</v>
+        <v>44.8</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>679.65</v>
+        <v>72.27</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>679.65</v>
+        <v>72.27</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>57.14</v>
+        <v>21.85</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>75.78</v>
+        <v>32.24</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>94.05</v>
+        <v>4.51</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.02</v>
+        <v>-4.87</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.47</v>
+        <v>-4.08</v>
       </c>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>133</v>
+        <v>39</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>7.5</v>
+        <v>15.4</v>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
@@ -3513,104 +3507,100 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>COMSYN</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Commercial Syn Bags Limited</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>AKCAPIT</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>AK Capital Services Limited</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n">
-        <v>1208</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>1746.4</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>1772.2</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>299.15</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>304.35</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>76.06999999999999</v>
-      </c>
-      <c r="O30" s="2" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>92.75</v>
-      </c>
-      <c r="Q30" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R30" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="W30" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="X30" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z30" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3610,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>KINGFA</t>
+          <t>BHAGYANGR</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Kingfa Science &amp; Technology (India) Limited</t>
+          <t>Bhagyanagar India Limited</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -3639,65 +3629,65 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>8420</v>
+        <v>1493</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>37.3</v>
+        <v>23.8</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>6197</v>
+        <v>446.7</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>6227.5</v>
+        <v>446.7</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>21.32</v>
+        <v>15.11</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>51.32</v>
+        <v>206.32</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>30.94</v>
+        <v>383.49</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n">
-        <v>32</v>
+        <v>386.4</v>
       </c>
       <c r="U31" s="3" t="n"/>
       <c r="V31" s="3" t="n">
-        <v>225</v>
+        <v>62</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>185</v>
+        <v>50</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>21.6</v>
+        <v>24</v>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
@@ -3717,608 +3707,620 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>TAALTECH</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Taal Tech Limited</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n">
-        <v>1679</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>5375.5</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>5375.5</v>
-      </c>
-      <c r="L32" s="2" t="n">
+      <c r="F32" s="3" t="n">
+        <v>4032</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>603.55</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>603.55</v>
+      </c>
+      <c r="L32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="U32" s="2" t="n"/>
-      <c r="V32" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="W32" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>219.54</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>367.65</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>217.62</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n">
+        <v>220.5</v>
+      </c>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>INVPRECQ</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Investment &amp; Precision Castings Limited</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>KAPSTON</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>1404</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>1405.8</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>1405.8</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
+      <c r="F33" s="2" t="n">
+        <v>1778</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>584.3</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>107.13</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>137.53</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA33" s="3" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>AEROPLANE</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Amir Chand Jagdish Kumar (Exports) Limited</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Filatex India Limited</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>2127</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>205.13</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>206.9</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>66.45999999999999</v>
-      </c>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n">
-        <v>13.96</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="Y34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="n">
+        <v>4166</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>130.65</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA34" s="3" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB34" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>DPEL</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>DPEL</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>1585</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>634.95</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>641.9</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="n">
-        <v>29.97</v>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>113.79</v>
-      </c>
-      <c r="P35" s="2" t="n">
-        <v>231.65</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R35" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S35" s="2" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="T35" s="2" t="n">
-        <v>232.7</v>
-      </c>
-      <c r="U35" s="2" t="n">
-        <v>233.4</v>
-      </c>
-      <c r="V35" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="W35" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="X35" s="2" t="n">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>YATHARTH</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Healthcare Index</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>1139.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>1139.5</v>
+      </c>
+      <c r="L35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>77.98</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>FCL</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Fineotex Chemical Limited</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>6708</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>57.72</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>58.71</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="O36" s="2" t="n">
-        <v>162.36</v>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>140.19</v>
-      </c>
-      <c r="Q36" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R36" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S36" s="2" t="n"/>
-      <c r="T36" s="2" t="n">
-        <v>141.2</v>
-      </c>
-      <c r="U36" s="2" t="n"/>
-      <c r="V36" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="W36" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="X36" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1577</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>217.19</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>244.81</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>247.7</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>248.8</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>SBC Exports Limited</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>KISSHT</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>OnEMI Technology Solutions Limited</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>2301</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>-0.72</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="P37" s="2" t="n">
-        <v>126.79</v>
-      </c>
-      <c r="Q37" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R37" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S37" s="2" t="n"/>
-      <c r="T37" s="2" t="n">
-        <v>127.8</v>
-      </c>
-      <c r="U37" s="2" t="n"/>
-      <c r="V37" s="2" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="W37" s="2" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="X37" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="n">
+        <v>6316</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="O37" s="3" t="n"/>
+      <c r="P37" s="3" t="n">
+        <v>70.66</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="S37" s="3" t="n"/>
+      <c r="T37" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="Z37" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -4328,84 +4330,84 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Limited</t>
+          <t>Sri Lotus Developers and Realty Limited</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>Nifty Realty</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>15473</v>
+        <v>10501</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>82.5</v>
+        <v>40.9</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1502</v>
+        <v>215.13</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1518.4</v>
+        <v>216.4</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-1.08</v>
+        <v>-0.59</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="N38" s="2" t="n">
-        <v>16.69</v>
+        <v>50.99</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>61.37</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>42.67</v>
+        <v>13.68</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>12.31</v>
+        <v>-8.08</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>43.7</v>
+        <v>16.6</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>30.4</v>
+        <v>21.8</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>173</v>
+        <v>243</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
@@ -4434,12 +4436,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>PCCL</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>MONOLITH</t>
+          <t>PCCL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4453,65 +4455,65 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>3114</v>
+        <v>1099</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>108</v>
+        <v>43.4</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1432.55</v>
+        <v>445</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1446.4</v>
+        <v>445</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N39" s="2" t="n">
-        <v>104.62</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>276.94</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>199.07</v>
+        <v>145.58</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>-0.47</v>
+        <v>-2.38</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>-1.75</v>
+        <v>-4.03</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>200.1</v>
+        <v>148.5</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>200.8</v>
+        <v>149.6</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
@@ -4520,12 +4522,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -4540,98 +4542,94 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>ROSSTECH</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ACCENTMIC</t>
+          <t>Rossell Techsys Limited</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1741</v>
+        <v>5178</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>39.7</v>
+        <v>196</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>725.75</v>
+        <v>1374.3</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>725.75</v>
+        <v>1374.3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N40" s="2" t="n">
-        <v>57.98</v>
+        <v>33.74</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>110.06</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>172.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S40" s="2" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>-2.38</v>
+      </c>
+      <c r="S40" s="2" t="n"/>
       <c r="T40" s="2" t="n">
-        <v>173.4</v>
-      </c>
-      <c r="U40" s="2" t="n">
-        <v>174.1</v>
-      </c>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="U40" s="2" t="n"/>
       <c r="V40" s="2" t="n">
-        <v>44</v>
+        <v>25.7</v>
       </c>
       <c r="W40" s="2" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -4646,412 +4644,108 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SEAMECLTD</t>
+          <t>AAYUSHBULL</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Seamec Limited</t>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>4534</v>
+        <v>1945</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>17.6</v>
+        <v>247</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>1283.65</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1788.4</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>1793.6</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
       <c r="N41" s="2" t="n">
-        <v>12.94</v>
+        <v>7.33</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>35.15</v>
+        <v>14.52</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>92.13</v>
+        <v>30.56</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>-1.02</v>
+        <v>-2.88</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S41" s="2" t="n"/>
+        <v>-2.38</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>-4.03</v>
+      </c>
       <c r="T41" s="2" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="U41" s="2" t="n"/>
+        <v>33.4</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>34.6</v>
+      </c>
       <c r="V41" s="2" t="n">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="W41" s="2" t="n">
-        <v>254</v>
+        <v>8</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>ROSSTECH</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Rossell Techsys Limited</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>4577</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1214.3</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>1218</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="n">
-        <v>21.99</v>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>77.41</v>
-      </c>
-      <c r="P42" s="2" t="n">
-        <v>72.87</v>
-      </c>
-      <c r="Q42" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R42" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S42" s="2" t="n"/>
-      <c r="T42" s="2" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U42" s="2" t="n"/>
-      <c r="V42" s="2" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W42" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="X42" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Rajputana Stainless Limited</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>1588</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J43" s="2" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="K43" s="2" t="n">
-        <v>190.21</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n">
-        <v>68.19</v>
-      </c>
-      <c r="Q43" s="2" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="R43" s="2" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="S43" s="2" t="n"/>
-      <c r="T43" s="2" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U43" s="2" t="n"/>
-      <c r="V43" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="W43" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="X43" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSHBULL</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>1930</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1260.2</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>1283.65</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>-1.83</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="O44" s="2" t="n">
-        <v>12.04</v>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>28.43</v>
-      </c>
-      <c r="Q44" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="R44" s="2" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="S44" s="2" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="T44" s="2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U44" s="2" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB44"/>
+  <autoFilter ref="A1:AB41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5085,7 +4779,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-11 (prices as of 2026-09-11)</t>
+          <t>2026-09-18 (prices as of 2026-09-18)</t>
         </is>
       </c>
     </row>
@@ -5097,7 +4791,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2541 NSE mainboard (EQ) + 1049 NSE Emerge SME</t>
+          <t>2551 NSE mainboard (EQ) + 1053 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -5133,7 +4827,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3590 screened -&gt; 201 at ATH -&gt; 198 outperforming -&gt; 91 record PAT -&gt; 43 in mcap band</t>
+          <t>3604 screened -&gt; 172 at ATH -&gt; 171 outperforming -&gt; 83 record PAT -&gt; 40 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,8 +84,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB41"/>
+  <dimension ref="A1:AB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,12 +636,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SAKAR</t>
+          <t>RPTECH</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Limited</t>
+          <t>Rashi Peripherals Limited</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -655,61 +655,61 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2625</v>
+        <v>5931</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>72.7</v>
+        <v>18.6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1179.8</v>
+        <v>893</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1179.8</v>
+        <v>902.85</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>-1.09</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>46.81</v>
+        <v>14.36</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>122.18</v>
+        <v>157.76</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>245.07</v>
+        <v>179.63</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n">
-        <v>247.9</v>
+        <v>181.4</v>
       </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n">
-        <v>36</v>
+        <v>326</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>31</v>
+        <v>283</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -728,107 +728,107 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>AVALON</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Avalon Technologies Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>PRECWIRE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>16947</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="F3" s="2" t="n">
+        <v>9222</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>2537.7</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>2537.7</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>45.46</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>166.59</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="n">
+        <v>502.6</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>507.35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>168.84</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -840,12 +840,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>FCL</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Shilpa Medicare Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -855,69 +855,65 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19991</v>
+        <v>7037</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70.3</v>
+        <v>57.5</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1021.1</v>
+        <v>60.48</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1021.1</v>
+        <v>60.48</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>85.2</v>
+        <v>47.87</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>215.89</v>
+        <v>199.85</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>149.78</v>
+        <v>146.54</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>11.84</v>
-      </c>
+        <v>-1.24</v>
+      </c>
+      <c r="S4" s="2" t="n"/>
       <c r="T4" s="2" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>137.9</v>
-      </c>
+        <v>148.4</v>
+      </c>
+      <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n">
-        <v>298</v>
+        <v>148</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>244</v>
+        <v>125</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>22.1</v>
+        <v>18.4</v>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
@@ -936,7 +932,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -946,12 +942,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MACPOWER</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>SBC Exports Limited</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -965,65 +961,65 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2105</v>
+        <v>2521</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>54.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2104.5</v>
+        <v>53.02</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2104.5</v>
+        <v>53.02</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>27.48</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>147.65</v>
+        <v>71.2</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>142.54</v>
+        <v>143.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n">
-        <v>145.4</v>
+        <v>144.9</v>
       </c>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n">
-        <v>38.9</v>
+        <v>38.2</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>34</v>
+        <v>31.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>14.4</v>
+        <v>22</v>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1038,7 +1034,7 @@
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KOVAI</t>
+          <t>MANINDS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Kovai Medical Center &amp; Hospital Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1067,65 +1063,65 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6779</v>
+        <v>7662</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>26.4</v>
+        <v>37.5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6226</v>
+        <v>1020.35</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6292</v>
+        <v>1020.35</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N6" s="2" t="n">
-        <v>6.56</v>
+        <v>79.28</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>141.63</v>
+        <v>209.62</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>141.63</v>
+        <v>140.34</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>22.27</v>
+        <v>-1.82</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>23.16</v>
+        <v>-1.24</v>
       </c>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="2" t="n">
-        <v>119.4</v>
+        <v>142.2</v>
       </c>
       <c r="U6" s="2" t="n"/>
       <c r="V6" s="2" t="n">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1140,7 +1136,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1150,17 +1146,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MENONBE</t>
+          <t>MACPOWER</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Menon Bearings Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Main (T2T)</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1169,65 +1165,65 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1772</v>
+        <v>2063</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>40.4</v>
+        <v>53</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>316.85</v>
+        <v>2062.5</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>321.4</v>
+        <v>2104.5</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-1.42</v>
+        <v>-2</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>80.61</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>168.27</v>
+        <v>149.62</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>139.31</v>
+        <v>139.59</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>142.2</v>
+        <v>141.4</v>
       </c>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1242,7 +1238,7 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1248,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>ANTELOPUS</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SBC Exports Limited</t>
+          <t>Antelopus Selan Energy Limited</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1271,65 +1267,65 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2343</v>
+        <v>4455</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61.3</v>
+        <v>31.8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49.24</v>
+        <v>1261.7</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>49.24</v>
+        <v>1261.7</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N8" s="2" t="n">
-        <v>12.96</v>
+        <v>56.13</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>55.77</v>
+        <v>138.01</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>130.31</v>
+        <v>128.09</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="2" t="n">
-        <v>133.2</v>
+        <v>129.9</v>
       </c>
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n">
-        <v>38.2</v>
+        <v>132</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>31.3</v>
+        <v>90</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>22</v>
+        <v>46.7</v>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1344,7 +1340,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1354,201 +1350,197 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AIRFLOA</t>
+          <t>TIMEX</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>AIRFLOA RAIL TECHNOLOGY LIMITE</t>
+          <t>Timex Group India Limited</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1400</v>
+        <v>7395</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>584.2</v>
+        <v>732.05</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>584.2</v>
+        <v>732.05</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>72.66</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>106.98</v>
-      </c>
+        <v>44.25</v>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n">
-        <v>109.17</v>
+        <v>112.47</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>-2.88</v>
+        <v>-0.91</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>-4.03</v>
-      </c>
+        <v>-0.24</v>
+      </c>
+      <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v>113.2</v>
-      </c>
+        <v>113.4</v>
+      </c>
+      <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>TIMEX</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Timex Group India Limited</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PGIL</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Pearl Global Industries Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>7208</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="F10" s="2" t="n">
+        <v>12265</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>714.2</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>714.2</v>
-      </c>
-      <c r="L10" s="3" t="n">
+      <c r="J10" s="2" t="n">
+        <v>1329.1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1329.1</v>
+      </c>
+      <c r="L10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>37.69</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n">
-        <v>107.28</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>104.27</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA10" s="3" t="inlineStr">
+      <c r="AA10" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1560,12 +1552,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>COMSYN</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Commercial Syn Bags Limited</t>
+          <t>Madhya Bharat Agro Products Limited</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1579,65 +1571,65 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1239</v>
+        <v>7381</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>41.7</v>
+        <v>47.6</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>306.55</v>
+        <v>168.47</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>306.55</v>
+        <v>169.52</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>46.06</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>99.81999999999999</v>
+        <v>82.66</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>97.34</v>
+        <v>102.29</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="2" t="n">
-        <v>100.2</v>
+        <v>104.1</v>
       </c>
       <c r="U11" s="2" t="n"/>
       <c r="V11" s="2" t="n">
-        <v>29.7</v>
+        <v>155</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1652,7 +1644,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1662,12 +1654,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Lumax Auto Technologies Limited</t>
+          <t>Filatex India Limited</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1677,69 +1669,65 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Nifty Auto</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>14318</v>
+        <v>4743</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43.2</v>
+        <v>24.8</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>2102.7</v>
+        <v>106.94</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2102.7</v>
+        <v>108.72</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-1.64</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>27.72</v>
+        <v>102.85</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>34.1</v>
+        <v>178.56</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>89.53</v>
+        <v>100.26</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>-0.73</v>
-      </c>
+        <v>-1.24</v>
+      </c>
+      <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>90.3</v>
-      </c>
+        <v>102.1</v>
+      </c>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n">
-        <v>383</v>
+        <v>192</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
@@ -1758,7 +1746,7 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1756,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>EBGNG</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GNG Electronics Limited</t>
+          <t>GHCL Textiles Limited</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1787,65 +1775,65 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8023</v>
+        <v>1330</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>56.3</v>
+        <v>13.8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>703.05</v>
+        <v>139.12</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>703.05</v>
+        <v>140.45</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>40.06</v>
+        <v>50.25</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>84.84</v>
+        <v>102.47</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>79.92</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="2" t="n">
-        <v>82.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="U13" s="2" t="n"/>
       <c r="V13" s="2" t="n">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>7.5</v>
+        <v>35.2</v>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1860,107 +1848,107 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>MWL</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Mangalam Worldwide Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>LLOYDSENGG</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>LLOYDS ENGINEERING WORKS LIMITED</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1262</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="F14" s="2" t="n">
+        <v>15290</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>43.04</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>-1.21</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>60.06</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="J14" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>152.46</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr">
+      <c r="AA14" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1972,12 +1960,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ELANTAS</t>
+          <t>ENGINERSIN</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Elantas Beck India Limited</t>
+          <t>Engineers India Limited</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1991,63 +1979,65 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>11235</v>
+        <v>17732</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>63.3</v>
+        <v>22.6</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14228</v>
+        <v>315.65</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>14513</v>
+        <v>315.65</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="O15" s="2" t="n"/>
+        <v>25.35</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>66.37</v>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>54.27</v>
+        <v>58.74</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>-0.66</v>
+        <v>-1.82</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-1.24</v>
       </c>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="2" t="n">
-        <v>54.9</v>
+        <v>60.6</v>
       </c>
       <c r="U15" s="2" t="n"/>
       <c r="V15" s="2" t="n">
-        <v>177</v>
+        <v>784</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>151</v>
+        <v>775</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>17.2</v>
+        <v>1.2</v>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2062,7 +2052,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2062,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CORONA Remedies Limited</t>
+          <t>Artemis Medicare Services Limited</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2087,69 +2077,65 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>13505</v>
+        <v>5661</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>63.6</v>
+        <v>48.8</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2201.8</v>
+        <v>357.7</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2236.1</v>
+        <v>357.7</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-1.53</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>17.83</v>
+        <v>37</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>33.4</v>
+        <v>65.66</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>53.07</v>
+        <v>48.61</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>-3.73</v>
+        <v>-1.82</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>-2.93</v>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>12.93</v>
-      </c>
+        <v>-1.24</v>
+      </c>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U16" s="2" t="n">
-        <v>40.1</v>
-      </c>
+        <v>50.4</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n">
-        <v>198</v>
+        <v>113</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
@@ -2168,7 +2154,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2164,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Alivus Life Sciences Limited</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2193,73 +2179,69 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17576</v>
+        <v>4695</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1430.8</v>
+        <v>159.12</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1443.7</v>
+        <v>159.12</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>33.68</v>
+        <v>43.75</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>50.64</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>51.11</v>
+        <v>35.56</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>11.84</v>
-      </c>
+        <v>-1.24</v>
+      </c>
+      <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>39.3</v>
-      </c>
+        <v>37.4</v>
+      </c>
+      <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="n">
-        <v>603</v>
+        <v>165</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>565</v>
+        <v>142</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>6.7</v>
+        <v>16.2</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2274,7 +2256,7 @@
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2266,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Limited</t>
+          <t>Amir Chand Jagdish Kumar (Exports) Limited</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2299,69 +2281,63 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nifty Healthcare Index</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>16047</v>
+        <v>2170</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1558.9</v>
+        <v>209.47</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1558.9</v>
+        <v>209.47</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>14.27</v>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>72.33</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n">
-        <v>49.12</v>
+        <v>16.37</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>-2.88</v>
+        <v>7.95</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <v>11.84</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="S18" s="2" t="n"/>
       <c r="T18" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="U18" s="2" t="n">
-        <v>37.3</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n">
-        <v>187</v>
+        <v>125</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>8.1</v>
+        <v>20.2</v>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
@@ -2380,7 +2356,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2366,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>AYE</t>
+          <t>AKCAPIT</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Aye Finance Limited</t>
+          <t>AK Capital Services Limited</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2409,65 +2385,61 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>4584</v>
+        <v>1144</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>19.3</v>
+        <v>9.99</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>185.72</v>
+        <v>1754</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>189.13</v>
+        <v>1772.2</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.03</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>72.68000000000001</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="n">
-        <v>44.07</v>
+        <v>-0.49</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>-2.69</v>
+        <v>-3.7</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>-1.81</v>
+        <v>-3.5</v>
       </c>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n">
-        <v>46.8</v>
+        <v>3.2</v>
       </c>
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="3" t="n">
-        <v>238</v>
+        <v>118</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>22.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2482,405 +2454,415 @@
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>VISHNU</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Vishnu Chemicals Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Spectrum Electrical Industries Limited</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>4864</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>722.15</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>731.55</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>43.78</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="n">
+        <v>6034</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3518.8</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>3518.8</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>96.68000000000001</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>138.79</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>146.07</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB20" s="3" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>SHUKRAPHAR</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Shukra Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2464</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n">
-        <v>35.03</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-3.02</v>
-      </c>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>KALYANI</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Kalyani Cast-Tech Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1392.05</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>1402.9</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>139.45</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>SAMBHV</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Sambhv Steel Tubes Limited</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SEDEMAC</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SEDEMAC Mechatronics Limited</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>4348</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>147.57</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>147.57</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="F22" s="2" t="n">
+        <v>15255</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>3444.9</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>3444.9</v>
+      </c>
+      <c r="L22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="U22" s="3" t="n"/>
-      <c r="V22" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>126.04</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr">
+      <c r="AA22" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB22" s="3" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>DRAGARWQ</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Dr Agarwals Eye Hospital Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>2565</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>5371.5</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>5422.5</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="n">
+        <v>2169</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>145.12</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>145.12</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>182.83</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="X23" s="2" t="n"/>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr">
+      <c r="AA23" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2892,84 +2874,84 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DPEL</t>
+          <t>The South Indian Bank Limited</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1619</v>
+        <v>13089</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>60.6</v>
+        <v>8.66</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>648.5</v>
+        <v>49.95</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>648.5</v>
+        <v>49.95</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N24" s="2" t="n">
-        <v>36.33</v>
+        <v>10</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>56.6</v>
+        <v>39.49</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>164.69</v>
+        <v>68.52</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>-2.38</v>
+        <v>-1.24</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>-4.03</v>
+        <v>-4.39</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>167.6</v>
+        <v>70.3</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>168.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>27</v>
+        <v>1511</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>27</v>
+        <v>1456</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
@@ -2978,329 +2960,321 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>SACHEEROME</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>SACHEEROME</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>1201</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>536.85</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>536.85</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>65.69</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>134.64</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA25" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SBCL</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Shivalik Bimetal Controls Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>6656</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1154.5</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>107.98</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>YASHHV</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Yash Highvoltage Limited</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>3166</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>1059.2</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>1080.45</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>126.32</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>117.94</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>120.8</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>GNA</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>GNA Axles Limited</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2657</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>617.65</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>620.45</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>41.44</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>94.23</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA26" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB26" s="3" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>QPOWER</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Quality Power Electrical Equipments Limited</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>STEELCAS</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Steelcast Limited</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>11904</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>1536.1</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>1536.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
+      <c r="F27" s="2" t="n">
+        <v>3818</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="L27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>84.06</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>55.34</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA27" s="3" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB27" s="3" t="inlineStr">
+      <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3312,12 +3286,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TAALTECH</t>
+          <t>SHANTIGOLD</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Taal Tech Limited</t>
+          <t>Shanti Gold International Limited</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3331,61 +3305,65 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1676</v>
+        <v>2498</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27</v>
+        <v>13.4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5416.3</v>
+        <v>325.68</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>5416.3</v>
+        <v>325.68</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>99.09999999999999</v>
+      </c>
       <c r="P28" s="2" t="n">
-        <v>29.08</v>
+        <v>51.9</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>-2.69</v>
+        <v>-1.82</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.24</v>
       </c>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="2" t="n">
-        <v>31.8</v>
+        <v>53.7</v>
       </c>
       <c r="U28" s="2" t="n"/>
       <c r="V28" s="2" t="n">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>57</v>
+        <v>161</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3400,409 +3378,409 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>ALGOQUANT</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Algoquant Fintech Limited</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>VINCOFE</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Vintage Coffee And Beverages Limited</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>2037</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>72.27</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="n">
+        <v>2697</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>184.15</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>185.77</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="U29" s="2" t="n"/>
+      <c r="V29" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA29" s="3" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB29" s="3" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>AKCAPIT</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>AK Capital Services Limited</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>INNOVACAP</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Innova Captab Limited</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>1746.4</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>1772.2</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>-2.55</v>
-      </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="n">
+        <v>7328</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1281</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>1297.6</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>90.81</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z30" s="3" t="inlineStr">
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA30" s="3" t="inlineStr">
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB30" s="3" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>BHAGYANGR</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Bhagyanagar India Limited</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>KINGFA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Kingfa Science &amp; Technology (India) Limited</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>1493</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>446.7</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>446.7</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>206.32</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>383.49</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n">
-        <v>386.4</v>
-      </c>
-      <c r="U31" s="3" t="n"/>
-      <c r="V31" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="n">
+        <v>8428</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>6237.5</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>6240.5</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46.17</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="U31" s="2" t="n"/>
+      <c r="V31" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA31" s="3" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
+      <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>TBZ</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>INVPRECQ</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Investment &amp; Precision Castings Limited</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>4032</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>603.55</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>603.55</v>
-      </c>
-      <c r="L32" s="3" t="n">
+      <c r="F32" s="2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>1480.6</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>1480.6</v>
+      </c>
+      <c r="L32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>219.54</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>367.65</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>217.62</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n">
-        <v>220.5</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n">
-        <v>215</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z32" s="3" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA32" s="3" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB32" s="3" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3814,99 +3792,103 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>KAPSTON</t>
+          <t>ZELIO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Kapston Services Limited</t>
+          <t>Zelio E Mobility Limited</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-BSE</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1778</v>
+        <v>2235</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>58.3</v>
+        <v>80.2</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>584.3</v>
+        <v>1056.9</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>588.4</v>
+        <v>1056.9</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N33" s="2" t="n">
-        <v>68.58</v>
+        <v>86.25</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>107.13</v>
+        <v>218.68</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>137.53</v>
+        <v>550</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>-2.88</v>
+        <v>-2.19</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S33" s="2" t="n"/>
+        <v>-1.55</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
       <c r="T33" s="2" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="U33" s="2" t="n"/>
+        <v>552.2</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>550.8</v>
+      </c>
       <c r="V33" s="2" t="n">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>28.1</v>
+        <v>28</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3916,80 +3898,84 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>AIMTRON</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Filatex India Limited</t>
+          <t>AIMTRON</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>SME-NSE</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SME Emerge</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>4166</v>
+        <v>4021</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.8</v>
+        <v>87.5</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>93.83</v>
+        <v>1890.25</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>93.83</v>
+        <v>1890.25</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="N34" s="2" t="n">
-        <v>71.04000000000001</v>
+        <v>48.41</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>130.65</v>
+        <v>127.88</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>64.33</v>
+        <v>167.23</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>-2.88</v>
+        <v>-1.82</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S34" s="2" t="n"/>
+        <v>-1.24</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>-1.54</v>
+      </c>
       <c r="T34" s="2" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="U34" s="2" t="n"/>
+        <v>169</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>168.8</v>
+      </c>
       <c r="V34" s="2" t="n">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>185</v>
+        <v>46</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
@@ -3998,227 +3984,219 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>half-yearly</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Mar 2026</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>YATHARTH</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Yatharth Hospital &amp; Trauma Care Services Limited</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SHADOWFAX</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Shadowfax Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Nifty Healthcare Index</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>1139.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>1139.5</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>77.98</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>44.38</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>171</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>16582</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>282.45</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>285.8</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>143.43</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>156.82</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA35" s="3" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB35" s="3" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>UTSSAV</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>UTSSAV</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>SME-NSE</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>1577</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>653.25</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>653.25</v>
-      </c>
-      <c r="L36" s="3" t="n">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SMSPHARMA</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>SMS Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>475</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>483.35</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="X36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>71.14</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>217.19</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>244.81</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>247.7</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>248.8</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>half-yearly</t>
-        </is>
-      </c>
-      <c r="AA36" s="3" t="inlineStr">
-        <is>
-          <t>Mar 2026</t>
-        </is>
-      </c>
-      <c r="AB36" s="3" t="inlineStr">
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4230,12 +4208,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>ALGOQUANT</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>OnEMI Technology Solutions Limited</t>
+          <t>Algoquant Fintech Limited</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -4249,59 +4227,61 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>6316</v>
+        <v>2030</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>19.9</v>
+        <v>44.7</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>356.05</v>
+        <v>72.28</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>359.95</v>
+        <v>73.37</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-1.08</v>
+        <v>-1.49</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>20.41</v>
-      </c>
-      <c r="O37" s="3" t="n"/>
+        <v>27.28</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>42.12</v>
+      </c>
       <c r="P37" s="3" t="n">
-        <v>70.66</v>
+        <v>4.53</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>-1.19</v>
+        <v>-5.86</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>-0.73</v>
+        <v>-5.01</v>
       </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n">
-        <v>71.8</v>
+        <v>10.4</v>
       </c>
       <c r="U37" s="3" t="n"/>
       <c r="V37" s="3" t="n">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>281</v>
+        <v>39</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>11.7</v>
+        <v>15.4</v>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
@@ -4320,432 +4300,330 @@
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>LOTUSDEV</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Sri Lotus Developers and Realty Limited</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Realty</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>10501</v>
-      </c>
-      <c r="G38" s="2" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>215.13</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>-0.59</v>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="O38" s="2" t="n">
-        <v>87.76000000000001</v>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="Q38" s="2" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R38" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S38" s="2" t="n">
-        <v>-8.08</v>
-      </c>
-      <c r="T38" s="2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U38" s="2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="V38" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="W38" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="X38" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z38" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1744</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>722.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>722.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>278.16</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>296.32</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>PCCL</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PCCL</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>SME-NSE</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n">
-        <v>1099</v>
-      </c>
-      <c r="G39" s="2" t="n">
+      <c r="F39" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G39" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>445</v>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>445</v>
-      </c>
-      <c r="L39" s="2" t="n">
+      <c r="I39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>445.3</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>453.05</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>86.70999999999999</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>153.08</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>154.6</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="X39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>83.34999999999999</v>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>80.93000000000001</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>145.58</v>
-      </c>
-      <c r="Q39" s="2" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R39" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S39" s="2" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="T39" s="2" t="n">
-        <v>148.5</v>
-      </c>
-      <c r="U39" s="2" t="n">
-        <v>149.6</v>
-      </c>
-      <c r="V39" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="W39" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="X39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z39" s="3" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
+      <c r="AB39" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>ROSSTECH</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Rossell Techsys Limited</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>5178</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>1374.3</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>1374.3</v>
-      </c>
-      <c r="L40" s="2" t="n">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>1302.25</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>1310.55</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>33.74</v>
-      </c>
-      <c r="O40" s="2" t="n">
-        <v>90.84999999999999</v>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="Q40" s="2" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R40" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S40" s="2" t="n"/>
-      <c r="T40" s="2" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="U40" s="2" t="n"/>
-      <c r="V40" s="2" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="W40" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="X40" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y40" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z40" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSHBULL</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>AAYUSH ART AND BULLION LIMITED</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>SME-BSE</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>SME Emerge</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>1945</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>1270.5</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>1283.65</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>30.56</v>
-      </c>
-      <c r="Q41" s="2" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="R41" s="2" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="S41" s="2" t="n">
-        <v>-4.03</v>
-      </c>
-      <c r="T41" s="2" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="U41" s="2" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="V41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="X41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z40" s="3" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
+      <c r="AB40" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB41"/>
+  <autoFilter ref="A1:AB40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4779,7 +4657,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-18 (prices as of 2026-09-18)</t>
+          <t>2026-09-25 (prices as of 2026-09-25)</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4669,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2551 NSE mainboard (EQ) + 1053 NSE Emerge SME</t>
+          <t>2558 NSE mainboard (EQ) + 1049 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4705,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3604 screened -&gt; 172 at ATH -&gt; 171 outperforming -&gt; 83 record PAT -&gt; 40 in mcap band</t>
+          <t>3607 screened -&gt; 178 at ATH -&gt; 174 outperforming -&gt; 80 record PAT -&gt; 39 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,8 +84,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,12 +636,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Knowledge Marine &amp; Engineering Works Limited</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -655,61 +655,61 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2878</v>
+        <v>8434</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>45</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>343.6</v>
+        <v>3327.7</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>345.45</v>
+        <v>3345.7</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>-0.54</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>83.81999999999999</v>
+        <v>38.37</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>131.02</v>
+        <v>87.87</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>121.51</v>
+        <v>194.51</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-5.38</v>
+        <v>-5.49</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-4.76</v>
+        <v>-4.87</v>
       </c>
       <c r="S2" s="2" t="n"/>
       <c r="T2" s="2" t="n">
-        <v>126.9</v>
+        <v>200</v>
       </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>4.7</v>
+        <v>65</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -728,407 +728,413 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>BLUSPRING</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Bluspring Enterprises Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RATNAVEER</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>2194</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="F3" s="2" t="n">
+        <v>2879</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>146.96</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>149.44</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>27.31</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>108.01</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>86.03</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>-23</v>
-      </c>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="J3" s="2" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>119.82</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>UNITEDPOLY</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>United Polyfab Gujarat Limited</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SHRINGARMS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Shringar House of Mangalsutra Limited</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>1148</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="F4" s="3" t="n">
+        <v>3027</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>80.48999999999999</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="U4" s="2" t="n"/>
-      <c r="V4" s="2" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X4" s="2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="n">
+        <v>313.83</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>317.74</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>FREDUN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Fredun Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GOODLUCK</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Goodluck India Limited</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>2563</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="F5" s="3" t="n">
+        <v>5907</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>1552.3</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>1552.3</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>-6.84</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n">
+      <c r="J5" s="3" t="n">
+        <v>593.05</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="W5" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="X5" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Z5" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>PREMIERPOL</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Premier Polyfilm Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ALGOQUANT</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Algoquant Fintech Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>1079</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>102.85</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>102.85</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>72.73</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>126.94</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n">
-        <v>132.3</v>
-      </c>
-      <c r="U6" s="2" t="n"/>
-      <c r="V6" s="2" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1140,17 +1146,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AKCAPIT</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AK Capital Services Limited</t>
+          <t>Nupur Recyclers Limited</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1159,57 +1165,61 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1154</v>
+        <v>1166</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10.1</v>
+        <v>68</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1751.7</v>
+        <v>168.85</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1772.2</v>
+        <v>168.85</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>203.96</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>-0.63</v>
+        <v>150.41</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>-6.84</v>
+        <v>-5.49</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-6.65</v>
+        <v>-4.87</v>
       </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n">
-        <v>6.2</v>
+        <v>155.9</v>
       </c>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n">
-        <v>118</v>
+        <v>19.8</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>114</v>
+        <v>16.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>3.5</v>
+        <v>20</v>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
@@ -1228,213 +1238,213 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SKYGOLD</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>SKY GOLD AND DIAMONDS LIMITED</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Nifty Consumer Durables</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>14269</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>921</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>921</v>
-      </c>
-      <c r="L8" s="2" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>PANACHE</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Panache Digilife Limited</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1051</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>656.45</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>656.45</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>132.95</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>194.2</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>-5.93</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <v>199.6</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>200.1</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>344</v>
-      </c>
-      <c r="W8" s="2" t="n">
-        <v>283</v>
-      </c>
-      <c r="X8" s="2" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>52.31</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>59.56</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Z8" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
+      <c r="AB8" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>KMEW</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge Marine &amp; Engineering Works Limited</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>8132</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>3207.8</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>3256.7</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>91.44</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>184.04</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n">
-        <v>189.4</v>
-      </c>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="X9" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sri Lotus Developers and Realty Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Nifty Realty</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>12080</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>246.25</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>246.25</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>75.95999999999999</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>75.98</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Z9" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1446,17 +1456,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SHANTIGOLD</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Shanti Gold International Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Main (T2T)</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1465,65 +1475,65 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2919</v>
+        <v>5055</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>15.7</v>
+        <v>23.6</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>380.55</v>
+        <v>759.15</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>380.55</v>
+        <v>759.15</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>63.27</v>
+        <v>194.1</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>94.81999999999999</v>
+        <v>406.54</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>81.34999999999999</v>
+        <v>303.61</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-5.38</v>
+        <v>-5.49</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-4.76</v>
+        <v>-4.87</v>
       </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n">
-        <v>86.7</v>
+        <v>309.1</v>
       </c>
       <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -1538,401 +1548,417 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>MMP</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>MMP Industries Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Wheels India Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>1274</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
+      <c r="F11" s="3" t="n">
+        <v>6593</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>501.35</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>501.35</v>
-      </c>
-      <c r="L11" s="2" t="n">
+      <c r="J11" s="3" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>2452.7</v>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>70.97</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>105.21</v>
-      </c>
-      <c r="P11" s="2" t="n">
-        <v>77.31</v>
-      </c>
-      <c r="Q11" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="W11" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>166.66</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Z11" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
+      <c r="AB11" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>DEEPA</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Deepa Jewellers Limited</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>2359</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
+      <c r="F12" s="3" t="n">
+        <v>6452</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>245.53</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>245.53</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="Q12" s="2" t="n">
-        <v>-5.36</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <v>-5.31</v>
-      </c>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="J12" s="3" t="n">
+        <v>208.71</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>211.95</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>83.11</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Z12" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
+      <c r="AB12" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>PRADPME</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Pradeep Metals Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ADVANCE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Advance Agrolife Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1092</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="F13" s="3" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="2" t="n">
-        <v>635.35</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>635.35</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="Q13" s="2" t="n">
-        <v>-6.84</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="W13" s="2" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="n">
+        <v>158.08</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>158.43</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
+      <c r="AB13" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>ONEGLOBAL</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>One Global Service Provider Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1132</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>VINYAS</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>VINYAS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>2108</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J14" s="2" t="n">
-        <v>576.4</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>585</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="Q14" s="2" t="n">
-        <v>-6.84</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="W14" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="X14" s="2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="n">
+        <v>1675.15</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>1675.15</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1944,84 +1970,80 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ZELIO</t>
+          <t>SVLL</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Zelio E Mobility Limited</t>
+          <t>Shree Vasu Logistics Limited</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>SME-BSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>2369</v>
+        <v>1013</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>142</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1119.9</v>
+        <v>881.45</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1119.9</v>
+        <v>881.45</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>85.08</v>
+        <v>18.27</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>196.58</v>
+        <v>47.08</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>556.0599999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>-5.92</v>
+        <v>-5.49</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>-1.66</v>
-      </c>
+        <v>-4.87</v>
+      </c>
+      <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n">
-        <v>562</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>557.7</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
@@ -2030,219 +2052,219 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Jun 2026</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>SHADOWFAX</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Shadowfax Technologies Limited</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AKCAPIT</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>AK Capital Services Limited</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>17303</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>294.85</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>294.85</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>30.06</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>130.56</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-5.27</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-4.28</v>
-      </c>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n">
-        <v>173.4</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1754</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1772.2</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="AB16" s="3" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>ONEPOINT</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>One Point One Solutions Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2115</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>80.36</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>80.36</v>
-      </c>
-      <c r="L17" s="2" t="n">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>UTSSAV</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>SME-NSE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2428</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1005.6</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1005.6</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>44.37</v>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>53.49</v>
-      </c>
-      <c r="P17" s="2" t="n">
-        <v>63.67</v>
-      </c>
-      <c r="Q17" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="W17" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="X17" s="2" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>consolidated</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>84.67</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>321.99</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>388.63</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2254,12 +2276,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>SAMBHV</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Amir Chand Jagdish Kumar (Exports) Limited</t>
+          <t>Sambhv Steel Tubes Limited</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -2273,61 +2295,61 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2273</v>
+        <v>5076</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>18.4</v>
+        <v>30.3</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>218.41</v>
+        <v>172.47</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>218.44</v>
+        <v>172.47</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>25.17</v>
+        <v>44.98</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>73.34</v>
+        <v>41.36</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>21.34</v>
+        <v>58.07</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>4.43</v>
+        <v>-5.49</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>5.35</v>
+        <v>-4.87</v>
       </c>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n">
-        <v>16.9</v>
+        <v>63.6</v>
       </c>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>20.2</v>
+        <v>16.2</v>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
@@ -2346,7 +2368,7 @@
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2356,12 +2378,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>TIMEX</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Timex Group India Limited</t>
+          <t>The South Indian Bank Limited</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2371,71 +2393,73 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Nifty Consumer Durables</t>
+          <t>Nifty Financial Services</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>7306</v>
+        <v>13488</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>724.4</v>
+        <v>51.45</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>734.6</v>
+        <v>51.48</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-1.39</v>
+        <v>-0.06</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O19" s="3" t="n"/>
+        <v>15.36</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>32.16</v>
+      </c>
       <c r="P19" s="3" t="n">
-        <v>110.25</v>
+        <v>56.15</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>-4.14</v>
+        <v>-5.49</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>-3.5</v>
+        <v>-4.87</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>-3.57</v>
+        <v>-7.28</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>114.4</v>
+        <v>61.6</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>113.8</v>
+        <v>63.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>85</v>
+        <v>1585</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>75</v>
+        <v>1511</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>13.3</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2445,221 +2469,739 @@
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>OCCLLTD</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>OCCL Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Main (T2T)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1097</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>218.54</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>218.54</v>
-      </c>
-      <c r="L20" s="2" t="n">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSHBULL</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>AAYUSH ART AND BULLION LIMITED</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SME-BSE</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>SME Emerge</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>1314.65</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>1314.65</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>73.55</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>124.53</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="Q20" s="2" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="U20" s="2" t="n"/>
-      <c r="V20" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="W20" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="X20" s="2" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>half-yearly</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>UNITEDPOLY</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>United Polyfab Gujarat Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1191</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>51.78</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SKY GOLD AND DIAMONDS LIMITED</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Consumer Durables</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>16405</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1060.6</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1060.6</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>70.70999999999999</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>224.94</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>344</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SHANTIGOLD</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>3239</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>423.3</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>423.3</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>99.09</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>112.49</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>100.26</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ONEPOINT</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>One Point One Solutions Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2238</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>84.98</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>85.79000000000001</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>AEROPLANE</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Amir Chand Jagdish Kumar (Exports) Limited</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>2431</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>234.78</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>234.78</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>SBC</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>SBC Exports Limited</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>2973</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="F26" s="2" t="n">
+        <v>3011</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>62.43</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>63.21</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>96.48999999999999</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>178.2</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="n">
-        <v>183.6</v>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y21" s="3" t="inlineStr">
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>91.68000000000001</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>174.16</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="n">
+        <v>179.7</v>
+      </c>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>consolidated</t>
         </is>
       </c>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA21" s="3" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="AB21" s="3" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB21"/>
+  <autoFilter ref="A1:AB26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2693,7 +3235,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09 (prices as of 2026-10-09)</t>
+          <t>2026-10-16 (prices as of 2026-10-16)</t>
         </is>
       </c>
     </row>
@@ -2705,7 +3247,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2574 NSE mainboard (EQ) + 1081 NSE Emerge SME</t>
+          <t>2575 NSE mainboard (EQ) + 1074 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -2741,7 +3283,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3655 screened -&gt; 105 at ATH -&gt; 104 outperforming -&gt; 43 record PAT -&gt; 20 in mcap band</t>
+          <t>3649 screened -&gt; 132 at ATH -&gt; 130 outperforming -&gt; 52 record PAT -&gt; 25 in mcap band</t>
         </is>
       </c>
     </row>

--- a/docs/ATH_Tracker_latest.xlsx
+++ b/docs/ATH_Tracker_latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ATH Screen'!$A$1:$AB$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -84,8 +84,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,203 +636,203 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>UTSSAV</t>
+          <t>SGMART</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UTSSAV</t>
+          <t>SG Mart Limited</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SME-NSE</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SME Emerge</t>
+          <t>Nifty Metal</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2449</v>
+        <v>10849</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41.5</v>
+        <v>71.5</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1014.25</v>
+        <v>856.35</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1019.6</v>
+        <v>864.55</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.95</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>96.18000000000001</v>
+        <v>24.92</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>314.23</v>
+        <v>51.41</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>413.54</v>
+        <v>131.66</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-9.369999999999999</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>-9.69</v>
+        <v>9.35</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>423.3</v>
+        <v>140.2</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>423.2</v>
+        <v>122.3</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>59</v>
+        <v>152</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>59</v>
+        <v>125</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>standalone</t>
+          <t>consolidated</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>half-yearly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>Mar 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>KROSS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Kross Limited</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NINSYS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>NINtec Systems Limited</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Main</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>1980</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>306.55</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>306.55</v>
-      </c>
-      <c r="L3" s="3" t="n">
+      <c r="F3" s="2" t="n">
+        <v>1748</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>939.6</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>939.6</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>standalone</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>112.03</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -844,12 +844,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SKY GOLD AND DIAMONDS LIMITED</t>
+          <t>Alivus Life Sciences Limited</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -859,73 +859,69 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nifty Consumer Durables</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>16186</v>
+        <v>17371</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48.3</v>
+        <v>25.2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1046.85</v>
+        <v>1415.3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1060.6</v>
+        <v>1443.7</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.97</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="N4" s="2" t="n">
-        <v>60.14</v>
+        <v>27.53</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>153.75</v>
+        <v>34.6</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>181.41</v>
+        <v>55.87</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>-13.08</v>
-      </c>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S4" s="2" t="n"/>
       <c r="T4" s="2" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>194.5</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n">
-        <v>344</v>
+        <v>670</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>283</v>
+        <v>603</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>21.6</v>
+        <v>11.1</v>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -935,12 +931,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -950,12 +946,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ALGOQUANT</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Algoquant Fintech Limited</t>
+          <t>Dr Agarwals Eye Hospital Limited</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -969,65 +965,61 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2099</v>
+        <v>2581</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46.2</v>
+        <v>33.9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>74.73</v>
+        <v>5317.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>74.73</v>
+        <v>5422.5</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>9.24</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>36.99</v>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n">
-        <v>8.07</v>
+        <v>-0.06</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>-10.76</v>
+        <v>-6.72</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-10.15</v>
+        <v>-6.8</v>
       </c>
       <c r="S5" s="2" t="n"/>
       <c r="T5" s="2" t="n">
-        <v>18.8</v>
+        <v>6.7</v>
       </c>
       <c r="U5" s="2" t="n"/>
       <c r="V5" s="2" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>15.4</v>
+        <v>7.1</v>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>consolidated</t>
+          <t>standalone</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1052,108 +1044,1136 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Spectrum Electrical Industries Limited</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6738</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>3954.1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>4013.7</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>232.76</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>MBAPL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Bharat Agro Products Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Chemicals</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>8127</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>177.11</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>177.11</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>-9.74</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SMSPHARMA</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SMS Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4788</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>511.35</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>511.35</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>The South Indian Bank Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Financial Services</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>14543</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>1585</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>1511</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>RATNAVEER</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3022</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>138.16</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n">
+        <v>146.8</v>
+      </c>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>KRISHANA</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Krishana Phoschem Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>7065</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>228.55</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>228.55</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>126.87</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="U11" s="2" t="n"/>
+      <c r="V11" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>standalone</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>3316</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>74.87</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>75.06</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n">
+        <v>80.76000000000001</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>LOTUSDEV</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Sri Lotus Developers and Realty Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Main (T2T)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Nifty Realty</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>12021</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>245.98</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>246.25</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>69.56</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>-14.37</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>SBC Exports Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3151</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>66.52</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>180.89</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>-8.59</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ALGOQUANT</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Algoquant Fintech Limited</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2141</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>76.22</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>76.43000000000001</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-8.81</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>AAYUSHBULL</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>AAYUSH ART AND BULLION LIMITED</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>SME-BSE</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>SME Emerge</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>254</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F16" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1306.2</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>1314.65</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>11.74</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="V6" s="2" t="n">
+      <c r="I16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1319.3</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>1322.15</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="V16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="W16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>standalone</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Z16" s="3" t="inlineStr">
         <is>
           <t>half-yearly</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Mar 2026</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
+      <c r="AB16" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB6"/>
+  <autoFilter ref="A1:AB16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1187,7 +2207,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-10-23 (prices as of 2026-10-23)</t>
+          <t>2026-10-30 (prices as of 2026-10-30)</t>
         </is>
       </c>
     </row>
@@ -1199,7 +2219,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2580 NSE mainboard (EQ) + 1073 NSE Emerge SME</t>
+          <t>2587 NSE mainboard (EQ) + 1065 NSE Emerge SME</t>
         </is>
       </c>
     </row>
@@ -1235,7 +2255,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>3653 screened -&gt; 34 at ATH -&gt; 32 outperforming -&gt; 12 record PAT -&gt; 5 in mcap band</t>
+          <t>3652 screened -&gt; 76 at ATH -&gt; 75 outperforming -&gt; 35 record PAT -&gt; 15 in mcap band</t>
         </is>
       </c>
     </row>
